--- a/research/traditional_assets/database/data/kazakhstan/kazakhstan_telecom_wireless.xlsx
+++ b/research/traditional_assets/database/data/kazakhstan/kazakhstan_telecom_wireless.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08692833615599665</v>
+        <v>0.08679047948368467</v>
       </c>
       <c r="C2">
-        <v>1624.946296218797</v>
+        <v>1614.434688611698</v>
       </c>
       <c r="D2">
-        <v>1607.246296218797</v>
+        <v>1612.651688611698</v>
       </c>
       <c r="E2">
-        <v>-283.4</v>
+        <v>-267.483</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>15.917</v>
       </c>
       <c r="G2">
         <v>17.7</v>
@@ -1445,28 +1445,28 @@
         <v>112.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.8006250999999999</v>
       </c>
       <c r="N2">
-        <v>112.5</v>
+        <v>111.6993749</v>
       </c>
       <c r="O2">
-        <v>22.5</v>
+        <v>22.33987498</v>
       </c>
       <c r="P2">
-        <v>90.00000000000001</v>
+        <v>89.35949992</v>
       </c>
       <c r="Q2">
-        <v>134.7</v>
+        <v>134.05949992</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08692833615599665</v>
+        <v>0.08726068634715622</v>
       </c>
       <c r="T2">
-        <v>0.6362422799549505</v>
+        <v>0.6413836317121623</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>140.5152049317465</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08679047948368467</v>
+        <v>0.08665262281137266</v>
       </c>
       <c r="C3">
-        <v>1614.434688611698</v>
+        <v>1603.959561864655</v>
       </c>
       <c r="D3">
-        <v>1612.651688611698</v>
+        <v>1618.093561864655</v>
       </c>
       <c r="E3">
-        <v>-267.483</v>
+        <v>-251.566</v>
       </c>
       <c r="F3">
-        <v>15.917</v>
+        <v>31.834</v>
       </c>
       <c r="G3">
         <v>17.7</v>
@@ -1527,28 +1527,28 @@
         <v>112.5</v>
       </c>
       <c r="M3">
-        <v>0.8006250999999999</v>
+        <v>1.6012502</v>
       </c>
       <c r="N3">
-        <v>111.6993749</v>
+        <v>110.8987498</v>
       </c>
       <c r="O3">
-        <v>22.33987498</v>
+        <v>22.17974996000001</v>
       </c>
       <c r="P3">
-        <v>89.35949992</v>
+        <v>88.71899984000001</v>
       </c>
       <c r="Q3">
-        <v>134.05949992</v>
+        <v>133.41899984</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08726068634715622</v>
+        <v>0.08759981919527823</v>
       </c>
       <c r="T3">
-        <v>0.6413836317121623</v>
+        <v>0.6466299090154395</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>140.5152049317465</v>
+        <v>70.25760246587325</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08665262281137266</v>
+        <v>0.08651476613906067</v>
       </c>
       <c r="C4">
-        <v>1603.959561864655</v>
+        <v>1593.521286540765</v>
       </c>
       <c r="D4">
-        <v>1618.093561864655</v>
+        <v>1623.572286540765</v>
       </c>
       <c r="E4">
-        <v>-251.566</v>
+        <v>-235.649</v>
       </c>
       <c r="F4">
-        <v>31.834</v>
+        <v>47.75099999999999</v>
       </c>
       <c r="G4">
         <v>17.7</v>
@@ -1609,28 +1609,28 @@
         <v>112.5</v>
       </c>
       <c r="M4">
-        <v>1.6012502</v>
+        <v>2.401875299999999</v>
       </c>
       <c r="N4">
-        <v>110.8987498</v>
+        <v>110.0981247</v>
       </c>
       <c r="O4">
-        <v>22.17974996000001</v>
+        <v>22.01962494</v>
       </c>
       <c r="P4">
-        <v>88.71899984000001</v>
+        <v>88.07849976000001</v>
       </c>
       <c r="Q4">
-        <v>133.41899984</v>
+        <v>132.77849976</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08759981919527823</v>
+        <v>0.08794594447325842</v>
       </c>
       <c r="T4">
-        <v>0.6466299090154395</v>
+        <v>0.6519843569847636</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>70.25760246587325</v>
+        <v>46.8384016439155</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08651476613906067</v>
+        <v>0.08637690946674868</v>
       </c>
       <c r="C5">
-        <v>1593.521286540765</v>
+        <v>1583.120238238957</v>
       </c>
       <c r="D5">
-        <v>1623.572286540765</v>
+        <v>1629.088238238956</v>
       </c>
       <c r="E5">
-        <v>-235.649</v>
+        <v>-219.732</v>
       </c>
       <c r="F5">
-        <v>47.75099999999999</v>
+        <v>63.66799999999999</v>
       </c>
       <c r="G5">
         <v>17.7</v>
@@ -1691,28 +1691,28 @@
         <v>112.5</v>
       </c>
       <c r="M5">
-        <v>2.401875299999999</v>
+        <v>3.202500399999999</v>
       </c>
       <c r="N5">
-        <v>110.0981247</v>
+        <v>109.2974996</v>
       </c>
       <c r="O5">
-        <v>22.01962494</v>
+        <v>21.85949992</v>
       </c>
       <c r="P5">
-        <v>88.07849976000001</v>
+        <v>87.43799968</v>
       </c>
       <c r="Q5">
-        <v>132.77849976</v>
+        <v>132.13799968</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08794594447325842</v>
+        <v>0.08829928069452989</v>
       </c>
       <c r="T5">
-        <v>0.6519843569847636</v>
+        <v>0.6574503559534489</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>46.8384016439155</v>
+        <v>35.12880123293662</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08637690946674868</v>
+        <v>0.08623905279443668</v>
       </c>
       <c r="C6">
-        <v>1583.120238238957</v>
+        <v>1572.756797679823</v>
       </c>
       <c r="D6">
-        <v>1629.088238238956</v>
+        <v>1634.641797679823</v>
       </c>
       <c r="E6">
-        <v>-219.732</v>
+        <v>-203.815</v>
       </c>
       <c r="F6">
-        <v>63.66799999999999</v>
+        <v>79.58499999999999</v>
       </c>
       <c r="G6">
         <v>17.7</v>
@@ -1773,28 +1773,28 @@
         <v>112.5</v>
       </c>
       <c r="M6">
-        <v>3.202500399999999</v>
+        <v>4.003125499999999</v>
       </c>
       <c r="N6">
-        <v>109.2974996</v>
+        <v>108.4968745</v>
       </c>
       <c r="O6">
-        <v>21.85949992</v>
+        <v>21.69937490000001</v>
       </c>
       <c r="P6">
-        <v>87.43799968</v>
+        <v>86.79749960000001</v>
       </c>
       <c r="Q6">
-        <v>132.13799968</v>
+        <v>131.4974996</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08829928069452989</v>
+        <v>0.08866005557309124</v>
       </c>
       <c r="T6">
-        <v>0.6574503559534489</v>
+        <v>0.6630314285846326</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>35.12880123293662</v>
+        <v>28.1030409863493</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08623905279443668</v>
+        <v>0.08610119612212469</v>
       </c>
       <c r="C7">
-        <v>1572.756797679823</v>
+        <v>1562.431350793219</v>
       </c>
       <c r="D7">
-        <v>1634.641797679823</v>
+        <v>1640.233350793219</v>
       </c>
       <c r="E7">
-        <v>-203.815</v>
+        <v>-187.898</v>
       </c>
       <c r="F7">
-        <v>79.58499999999999</v>
+        <v>95.502</v>
       </c>
       <c r="G7">
         <v>17.7</v>
@@ -1855,28 +1855,28 @@
         <v>112.5</v>
       </c>
       <c r="M7">
-        <v>4.003125499999999</v>
+        <v>4.8037506</v>
       </c>
       <c r="N7">
-        <v>108.4968745</v>
+        <v>107.6962494</v>
       </c>
       <c r="O7">
-        <v>21.69937490000001</v>
+        <v>21.53924988</v>
       </c>
       <c r="P7">
-        <v>86.79749960000001</v>
+        <v>86.15699952000001</v>
       </c>
       <c r="Q7">
-        <v>131.4974996</v>
+        <v>130.85699952</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08866005557309124</v>
+        <v>0.08902850651289862</v>
       </c>
       <c r="T7">
-        <v>0.6630314285846326</v>
+        <v>0.6687312474420118</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>28.1030409863493</v>
+        <v>23.41920082195774</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08610119612212469</v>
+        <v>0.08596333944981269</v>
       </c>
       <c r="C8">
-        <v>1562.431350793219</v>
+        <v>1552.144288807663</v>
       </c>
       <c r="D8">
-        <v>1640.233350793219</v>
+        <v>1645.863288807662</v>
       </c>
       <c r="E8">
-        <v>-187.898</v>
+        <v>-171.981</v>
       </c>
       <c r="F8">
-        <v>95.50199999999998</v>
+        <v>111.419</v>
       </c>
       <c r="G8">
         <v>17.7</v>
@@ -1937,28 +1937,28 @@
         <v>112.5</v>
       </c>
       <c r="M8">
-        <v>4.803750599999999</v>
+        <v>5.604375699999999</v>
       </c>
       <c r="N8">
-        <v>107.6962494</v>
+        <v>106.8956243</v>
       </c>
       <c r="O8">
-        <v>21.53924988</v>
+        <v>21.37912486</v>
       </c>
       <c r="P8">
-        <v>86.15699952000001</v>
+        <v>85.51649944</v>
       </c>
       <c r="Q8">
-        <v>130.85699952</v>
+        <v>130.21649944</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08902850651289862</v>
+        <v>0.08940488112883085</v>
       </c>
       <c r="T8">
-        <v>0.6687312474420118</v>
+        <v>0.6745536430490121</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>23.41920082195775</v>
+        <v>20.07360070453521</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08596333944981269</v>
+        <v>0.08582548277750071</v>
       </c>
       <c r="C9">
-        <v>1552.144288807662</v>
+        <v>1541.896008341584</v>
       </c>
       <c r="D9">
-        <v>1645.863288807662</v>
+        <v>1651.532008341584</v>
       </c>
       <c r="E9">
-        <v>-171.981</v>
+        <v>-156.064</v>
       </c>
       <c r="F9">
-        <v>111.419</v>
+        <v>127.336</v>
       </c>
       <c r="G9">
         <v>17.7</v>
@@ -2019,28 +2019,28 @@
         <v>112.5</v>
       </c>
       <c r="M9">
-        <v>5.604375699999999</v>
+        <v>6.405000799999999</v>
       </c>
       <c r="N9">
-        <v>106.8956243</v>
+        <v>106.0949992</v>
       </c>
       <c r="O9">
-        <v>21.37912486</v>
+        <v>21.21899984000001</v>
       </c>
       <c r="P9">
-        <v>85.51649944</v>
+        <v>84.87599936000001</v>
       </c>
       <c r="Q9">
-        <v>130.21649944</v>
+        <v>129.57599936</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08940488112883085</v>
+        <v>0.08978943780163121</v>
       </c>
       <c r="T9">
-        <v>0.6745536430490121</v>
+        <v>0.6805026124735558</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.07360070453521</v>
+        <v>17.56440061646831</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08582548277750071</v>
+        <v>0.08568762610518871</v>
       </c>
       <c r="C10">
-        <v>1541.896008341584</v>
+        <v>1531.686911496471</v>
       </c>
       <c r="D10">
-        <v>1651.532008341584</v>
+        <v>1657.239911496471</v>
       </c>
       <c r="E10">
-        <v>-156.064</v>
+        <v>-140.147</v>
       </c>
       <c r="F10">
-        <v>127.336</v>
+        <v>143.253</v>
       </c>
       <c r="G10">
         <v>17.7</v>
@@ -2101,28 +2101,28 @@
         <v>112.5</v>
       </c>
       <c r="M10">
-        <v>6.405000799999999</v>
+        <v>7.205625899999999</v>
       </c>
       <c r="N10">
-        <v>106.0949992</v>
+        <v>105.2943741</v>
       </c>
       <c r="O10">
-        <v>21.21899984000001</v>
+        <v>21.05887482</v>
       </c>
       <c r="P10">
-        <v>84.87599936000001</v>
+        <v>84.23549928000001</v>
       </c>
       <c r="Q10">
-        <v>129.57599936</v>
+        <v>128.93549928</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08978943780163121</v>
+        <v>0.09018244626943814</v>
       </c>
       <c r="T10">
-        <v>0.6805026124735558</v>
+        <v>0.6865823284788587</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.56440061646831</v>
+        <v>15.61280054797183</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08568762610518871</v>
+        <v>0.08554976943287672</v>
       </c>
       <c r="C11">
-        <v>1531.686911496471</v>
+        <v>1521.517405951937</v>
       </c>
       <c r="D11">
-        <v>1657.239911496471</v>
+        <v>1662.987405951937</v>
       </c>
       <c r="E11">
-        <v>-140.147</v>
+        <v>-124.23</v>
       </c>
       <c r="F11">
-        <v>143.253</v>
+        <v>159.17</v>
       </c>
       <c r="G11">
         <v>17.7</v>
@@ -2183,28 +2183,28 @@
         <v>112.5</v>
       </c>
       <c r="M11">
-        <v>7.205625899999999</v>
+        <v>8.006250999999997</v>
       </c>
       <c r="N11">
-        <v>105.2943741</v>
+        <v>104.493749</v>
       </c>
       <c r="O11">
-        <v>21.05887482</v>
+        <v>20.8987498</v>
       </c>
       <c r="P11">
-        <v>84.23549928000001</v>
+        <v>83.59499920000002</v>
       </c>
       <c r="Q11">
-        <v>128.93549928</v>
+        <v>128.2949992</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09018244626943814</v>
+        <v>0.0905841882587519</v>
       </c>
       <c r="T11">
-        <v>0.6865823284788587</v>
+        <v>0.6927971492842794</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.61280054797183</v>
+        <v>14.05152049317465</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08554976943287673</v>
+        <v>0.08554391276056474</v>
       </c>
       <c r="C12">
-        <v>1521.517405951936</v>
+        <v>1505.845464166368</v>
       </c>
       <c r="D12">
-        <v>1662.987405951936</v>
+        <v>1663.232464166368</v>
       </c>
       <c r="E12">
-        <v>-124.23</v>
+        <v>-108.313</v>
       </c>
       <c r="F12">
-        <v>159.17</v>
+        <v>175.087</v>
       </c>
       <c r="G12">
         <v>17.7</v>
@@ -2265,45 +2265,45 @@
         <v>112.5</v>
       </c>
       <c r="M12">
-        <v>8.006250999999999</v>
+        <v>9.069506599999999</v>
       </c>
       <c r="N12">
-        <v>104.493749</v>
+        <v>103.4304934</v>
       </c>
       <c r="O12">
-        <v>20.8987498</v>
+        <v>20.68609868</v>
       </c>
       <c r="P12">
-        <v>83.5949992</v>
+        <v>82.74439472000002</v>
       </c>
       <c r="Q12">
-        <v>128.2949992</v>
+        <v>127.44439472</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09058418825875192</v>
+        <v>0.0909949581579379</v>
       </c>
       <c r="T12">
-        <v>0.6927971492842796</v>
+        <v>0.699151628984204</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>14.05152049317465</v>
+        <v>12.40420289236021</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08554391276056474</v>
+        <v>0.08541805608825274</v>
       </c>
       <c r="C13">
-        <v>1505.845464166368</v>
+        <v>1495.21213842729</v>
       </c>
       <c r="D13">
-        <v>1663.232464166368</v>
+        <v>1668.51613842729</v>
       </c>
       <c r="E13">
-        <v>-108.313</v>
+        <v>-92.39600000000002</v>
       </c>
       <c r="F13">
-        <v>175.087</v>
+        <v>191.004</v>
       </c>
       <c r="G13">
         <v>17.7</v>
@@ -2347,28 +2347,28 @@
         <v>112.5</v>
       </c>
       <c r="M13">
-        <v>9.069506599999999</v>
+        <v>9.894007199999997</v>
       </c>
       <c r="N13">
-        <v>103.4304934</v>
+        <v>102.6059928</v>
       </c>
       <c r="O13">
-        <v>20.68609868</v>
+        <v>20.52119856000001</v>
       </c>
       <c r="P13">
-        <v>82.74439472000002</v>
+        <v>82.08479424000002</v>
       </c>
       <c r="Q13">
-        <v>127.44439472</v>
+        <v>126.78479424</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0909949581579379</v>
+        <v>0.09141506373665084</v>
       </c>
       <c r="T13">
-        <v>0.699151628984204</v>
+        <v>0.7056505286773088</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.40420289236021</v>
+        <v>11.37051931799686</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08541805608825274</v>
+        <v>0.08529219941594074</v>
       </c>
       <c r="C14">
-        <v>1495.21213842729</v>
+        <v>1484.612489498817</v>
       </c>
       <c r="D14">
-        <v>1668.51613842729</v>
+        <v>1673.833489498817</v>
       </c>
       <c r="E14">
-        <v>-92.39600000000002</v>
+        <v>-76.47899999999998</v>
       </c>
       <c r="F14">
-        <v>191.004</v>
+        <v>206.921</v>
       </c>
       <c r="G14">
         <v>17.7</v>
@@ -2429,28 +2429,28 @@
         <v>112.5</v>
       </c>
       <c r="M14">
-        <v>9.894007199999997</v>
+        <v>10.7185078</v>
       </c>
       <c r="N14">
-        <v>102.6059928</v>
+        <v>101.7814922</v>
       </c>
       <c r="O14">
-        <v>20.52119856000001</v>
+        <v>20.35629844</v>
       </c>
       <c r="P14">
-        <v>82.08479424000002</v>
+        <v>81.42519376000001</v>
       </c>
       <c r="Q14">
-        <v>126.78479424</v>
+        <v>126.12519376</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09141506373665084</v>
+        <v>0.09184482691487442</v>
       </c>
       <c r="T14">
-        <v>0.7056505286773088</v>
+        <v>0.7122988283633583</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.37051931799686</v>
+        <v>10.49586398584326</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08529219941594074</v>
+        <v>0.08535674274362874</v>
       </c>
       <c r="C15">
-        <v>1484.612489498817</v>
+        <v>1465.964355034384</v>
       </c>
       <c r="D15">
-        <v>1673.833489498817</v>
+        <v>1671.102355034383</v>
       </c>
       <c r="E15">
-        <v>-76.47899999999998</v>
+        <v>-60.56199999999998</v>
       </c>
       <c r="F15">
-        <v>206.921</v>
+        <v>222.838</v>
       </c>
       <c r="G15">
         <v>17.7</v>
@@ -2511,45 +2511,45 @@
         <v>112.5</v>
       </c>
       <c r="M15">
-        <v>10.7185078</v>
+        <v>11.921833</v>
       </c>
       <c r="N15">
-        <v>101.7814922</v>
+        <v>100.578167</v>
       </c>
       <c r="O15">
-        <v>20.35629844</v>
+        <v>20.1156334</v>
       </c>
       <c r="P15">
-        <v>81.42519376000001</v>
+        <v>80.4625336</v>
       </c>
       <c r="Q15">
-        <v>126.12519376</v>
+        <v>125.1625336</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09184482691487442</v>
+        <v>0.09228458458561482</v>
       </c>
       <c r="T15">
-        <v>0.7122988283633583</v>
+        <v>0.7191017396700139</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>10.49586398584326</v>
+        <v>9.43646836858057</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08535674274362874</v>
+        <v>0.08524448607131674</v>
       </c>
       <c r="C16">
-        <v>1465.964355034384</v>
+        <v>1454.803213410374</v>
       </c>
       <c r="D16">
-        <v>1671.102355034383</v>
+        <v>1675.858213410374</v>
       </c>
       <c r="E16">
-        <v>-60.56199999999998</v>
+        <v>-44.64499999999998</v>
       </c>
       <c r="F16">
-        <v>222.838</v>
+        <v>238.755</v>
       </c>
       <c r="G16">
         <v>17.7</v>
@@ -2593,28 +2593,28 @@
         <v>112.5</v>
       </c>
       <c r="M16">
-        <v>11.921833</v>
+        <v>12.7733925</v>
       </c>
       <c r="N16">
-        <v>100.578167</v>
+        <v>99.72660750000001</v>
       </c>
       <c r="O16">
-        <v>20.1156334</v>
+        <v>19.94532150000001</v>
       </c>
       <c r="P16">
-        <v>80.4625336</v>
+        <v>79.78128600000001</v>
       </c>
       <c r="Q16">
-        <v>125.1625336</v>
+        <v>124.481286</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09228458458561482</v>
+        <v>0.09273468949566677</v>
       </c>
       <c r="T16">
-        <v>0.7191017396700139</v>
+        <v>0.7260647194780023</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.43646836858057</v>
+        <v>8.807370477341866</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08524448607131674</v>
+        <v>0.08513222939900475</v>
       </c>
       <c r="C17">
-        <v>1454.803213410374</v>
+        <v>1443.669218828036</v>
       </c>
       <c r="D17">
-        <v>1675.858213410374</v>
+        <v>1680.641218828036</v>
       </c>
       <c r="E17">
-        <v>-44.64500000000001</v>
+        <v>-28.72800000000001</v>
       </c>
       <c r="F17">
-        <v>238.755</v>
+        <v>254.672</v>
       </c>
       <c r="G17">
         <v>17.7</v>
@@ -2675,28 +2675,28 @@
         <v>112.5</v>
       </c>
       <c r="M17">
-        <v>12.7733925</v>
+        <v>13.624952</v>
       </c>
       <c r="N17">
-        <v>99.72660750000001</v>
+        <v>98.87504800000002</v>
       </c>
       <c r="O17">
-        <v>19.94532150000001</v>
+        <v>19.7750096</v>
       </c>
       <c r="P17">
-        <v>79.78128600000001</v>
+        <v>79.10003840000002</v>
       </c>
       <c r="Q17">
-        <v>124.481286</v>
+        <v>123.8000384</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09273468949566677</v>
+        <v>0.09319551118929137</v>
       </c>
       <c r="T17">
-        <v>0.7260647194780023</v>
+        <v>0.7331934845195144</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.807370477341866</v>
+        <v>8.256909822508</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08513222939900475</v>
+        <v>0.08501997272669276</v>
       </c>
       <c r="C18">
-        <v>1443.669218828036</v>
+        <v>1432.562604390788</v>
       </c>
       <c r="D18">
-        <v>1680.641218828036</v>
+        <v>1685.451604390787</v>
       </c>
       <c r="E18">
-        <v>-28.72800000000001</v>
+        <v>-12.81099999999998</v>
       </c>
       <c r="F18">
-        <v>254.672</v>
+        <v>270.589</v>
       </c>
       <c r="G18">
         <v>17.7</v>
@@ -2757,28 +2757,28 @@
         <v>112.5</v>
       </c>
       <c r="M18">
-        <v>13.624952</v>
+        <v>14.4765115</v>
       </c>
       <c r="N18">
-        <v>98.87504800000002</v>
+        <v>98.02348850000001</v>
       </c>
       <c r="O18">
-        <v>19.7750096</v>
+        <v>19.6046977</v>
       </c>
       <c r="P18">
-        <v>79.10003840000002</v>
+        <v>78.41879080000001</v>
       </c>
       <c r="Q18">
-        <v>123.8000384</v>
+        <v>123.1187908</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09319551118929137</v>
+        <v>0.09366743702011177</v>
       </c>
       <c r="T18">
-        <v>0.7331934845195144</v>
+        <v>0.7404940270319063</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.256909822508</v>
+        <v>7.771209244713412</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08501997272669276</v>
+        <v>0.08502291605438078</v>
       </c>
       <c r="C19">
-        <v>1432.562604390788</v>
+        <v>1416.519126380658</v>
       </c>
       <c r="D19">
-        <v>1685.451604390787</v>
+        <v>1685.325126380658</v>
       </c>
       <c r="E19">
-        <v>-12.81099999999998</v>
+        <v>3.106000000000051</v>
       </c>
       <c r="F19">
-        <v>270.589</v>
+        <v>286.506</v>
       </c>
       <c r="G19">
         <v>17.7</v>
@@ -2839,45 +2839,45 @@
         <v>112.5</v>
       </c>
       <c r="M19">
-        <v>14.4765115</v>
+        <v>15.5572758</v>
       </c>
       <c r="N19">
-        <v>98.02348850000001</v>
+        <v>96.94272420000001</v>
       </c>
       <c r="O19">
-        <v>19.6046977</v>
+        <v>19.38854484000001</v>
       </c>
       <c r="P19">
-        <v>78.41879080000001</v>
+        <v>77.55417936000001</v>
       </c>
       <c r="Q19">
-        <v>123.1187908</v>
+        <v>122.25417936</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09366743702011177</v>
+        <v>0.09415087323704974</v>
       </c>
       <c r="T19">
-        <v>0.7404940270319063</v>
+        <v>0.7479726315567956</v>
       </c>
       <c r="U19">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>7.771209244713412</v>
+        <v>7.23134316356338</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08502291605438078</v>
+        <v>0.0849170593820688</v>
       </c>
       <c r="C20">
-        <v>1416.519126380658</v>
+        <v>1405.162870783757</v>
       </c>
       <c r="D20">
-        <v>1685.325126380658</v>
+        <v>1689.885870783757</v>
       </c>
       <c r="E20">
-        <v>3.105999999999995</v>
+        <v>19.02299999999997</v>
       </c>
       <c r="F20">
-        <v>286.506</v>
+        <v>302.4229999999999</v>
       </c>
       <c r="G20">
         <v>17.7</v>
@@ -2921,28 +2921,28 @@
         <v>112.5</v>
       </c>
       <c r="M20">
-        <v>15.5572758</v>
+        <v>16.4215689</v>
       </c>
       <c r="N20">
-        <v>96.94272420000001</v>
+        <v>96.07843110000002</v>
       </c>
       <c r="O20">
-        <v>19.38854484000001</v>
+        <v>19.21568622000001</v>
       </c>
       <c r="P20">
-        <v>77.55417936000001</v>
+        <v>76.86274488000001</v>
       </c>
       <c r="Q20">
-        <v>122.25417936</v>
+        <v>121.56274488</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09415087323704972</v>
+        <v>0.0946462461507022</v>
       </c>
       <c r="T20">
-        <v>0.7479726315567955</v>
+        <v>0.755635892983534</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.23134316356338</v>
+        <v>6.850746154954782</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0849170593820688</v>
+        <v>0.0848112027097568</v>
       </c>
       <c r="C21">
-        <v>1405.162870783757</v>
+        <v>1393.831366293832</v>
       </c>
       <c r="D21">
-        <v>1689.885870783757</v>
+        <v>1694.471366293832</v>
       </c>
       <c r="E21">
-        <v>19.02299999999997</v>
+        <v>34.94</v>
       </c>
       <c r="F21">
-        <v>302.4229999999999</v>
+        <v>318.34</v>
       </c>
       <c r="G21">
         <v>17.7</v>
@@ -3003,28 +3003,28 @@
         <v>112.5</v>
       </c>
       <c r="M21">
-        <v>16.4215689</v>
+        <v>17.285862</v>
       </c>
       <c r="N21">
-        <v>96.07843110000002</v>
+        <v>95.21413800000002</v>
       </c>
       <c r="O21">
-        <v>19.21568622000001</v>
+        <v>19.04282760000001</v>
       </c>
       <c r="P21">
-        <v>76.86274488000001</v>
+        <v>76.17131040000001</v>
       </c>
       <c r="Q21">
-        <v>121.56274488</v>
+        <v>120.8713104</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.0946462461507022</v>
+        <v>0.09515400338719598</v>
       </c>
       <c r="T21">
-        <v>0.755635892983534</v>
+        <v>0.7634907359459406</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.850746154954782</v>
+        <v>6.508208847207043</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0848112027097568</v>
+        <v>0.0847053460374448</v>
       </c>
       <c r="C22">
-        <v>1393.831366293832</v>
+        <v>1382.524814945058</v>
       </c>
       <c r="D22">
-        <v>1694.471366293832</v>
+        <v>1699.081814945058</v>
       </c>
       <c r="E22">
-        <v>34.94</v>
+        <v>50.85700000000003</v>
       </c>
       <c r="F22">
-        <v>318.34</v>
+        <v>334.257</v>
       </c>
       <c r="G22">
         <v>17.7</v>
@@ -3085,28 +3085,28 @@
         <v>112.5</v>
       </c>
       <c r="M22">
-        <v>17.285862</v>
+        <v>18.1501551</v>
       </c>
       <c r="N22">
-        <v>95.21413800000002</v>
+        <v>94.34984490000002</v>
       </c>
       <c r="O22">
-        <v>19.04282760000001</v>
+        <v>18.86996898000001</v>
       </c>
       <c r="P22">
-        <v>76.17131040000001</v>
+        <v>75.47987592000001</v>
       </c>
       <c r="Q22">
-        <v>120.8713104</v>
+        <v>120.17987592</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09515400338719598</v>
+        <v>0.09567461523727189</v>
       </c>
       <c r="T22">
-        <v>0.7634907359459406</v>
+        <v>0.7715444356922059</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.508208847207043</v>
+        <v>6.198294140197183</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0847053460374448</v>
+        <v>0.08477548936513281</v>
       </c>
       <c r="C23">
-        <v>1382.524814945059</v>
+        <v>1363.55001491597</v>
       </c>
       <c r="D23">
-        <v>1699.081814945058</v>
+        <v>1696.02401491597</v>
       </c>
       <c r="E23">
-        <v>50.85699999999997</v>
+        <v>66.774</v>
       </c>
       <c r="F23">
-        <v>334.2569999999999</v>
+        <v>350.174</v>
       </c>
       <c r="G23">
         <v>17.7</v>
@@ -3167,45 +3167,45 @@
         <v>112.5</v>
       </c>
       <c r="M23">
-        <v>18.1501551</v>
+        <v>19.3646222</v>
       </c>
       <c r="N23">
-        <v>94.34984490000002</v>
+        <v>93.13537780000001</v>
       </c>
       <c r="O23">
-        <v>18.86996898000001</v>
+        <v>18.62707556000001</v>
       </c>
       <c r="P23">
-        <v>75.47987592000001</v>
+        <v>74.50830224000001</v>
       </c>
       <c r="Q23">
-        <v>120.17987592</v>
+        <v>119.20830224</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09567461523727189</v>
+        <v>0.09620857610914463</v>
       </c>
       <c r="T23">
-        <v>0.7715444356922059</v>
+        <v>0.7798046405601702</v>
       </c>
       <c r="U23">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V23">
         <v>0.2</v>
       </c>
       <c r="W23">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y23">
-        <v>6.198294140197183</v>
+        <v>5.809563379966175</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08477548936513281</v>
+        <v>0.0846776326928208</v>
       </c>
       <c r="C24">
-        <v>1363.55001491597</v>
+        <v>1351.901980250672</v>
       </c>
       <c r="D24">
-        <v>1696.02401491597</v>
+        <v>1700.292980250672</v>
       </c>
       <c r="E24">
-        <v>66.774</v>
+        <v>82.69099999999997</v>
       </c>
       <c r="F24">
-        <v>350.174</v>
+        <v>366.091</v>
       </c>
       <c r="G24">
         <v>17.7</v>
@@ -3249,28 +3249,28 @@
         <v>112.5</v>
       </c>
       <c r="M24">
-        <v>19.3646222</v>
+        <v>20.2448323</v>
       </c>
       <c r="N24">
-        <v>93.13537780000001</v>
+        <v>92.25516770000002</v>
       </c>
       <c r="O24">
-        <v>18.62707556000001</v>
+        <v>18.45103354</v>
       </c>
       <c r="P24">
-        <v>74.50830224000001</v>
+        <v>73.80413416000002</v>
       </c>
       <c r="Q24">
-        <v>119.20830224</v>
+        <v>118.50413416</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09620857610914463</v>
+        <v>0.09675640609457248</v>
       </c>
       <c r="T24">
-        <v>0.7798046405601702</v>
+        <v>0.7882793962039257</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.809563379966175</v>
+        <v>5.556973667793732</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0846776326928208</v>
+        <v>0.08457977602050883</v>
       </c>
       <c r="C25">
-        <v>1351.901980250672</v>
+        <v>1340.275490152399</v>
       </c>
       <c r="D25">
-        <v>1700.292980250672</v>
+        <v>1704.583490152399</v>
       </c>
       <c r="E25">
-        <v>82.69099999999997</v>
+        <v>98.608</v>
       </c>
       <c r="F25">
-        <v>366.091</v>
+        <v>382.008</v>
       </c>
       <c r="G25">
         <v>17.7</v>
@@ -3331,28 +3331,28 @@
         <v>112.5</v>
       </c>
       <c r="M25">
-        <v>20.2448323</v>
+        <v>21.1250424</v>
       </c>
       <c r="N25">
-        <v>92.25516770000002</v>
+        <v>91.37495760000002</v>
       </c>
       <c r="O25">
-        <v>18.45103354</v>
+        <v>18.27499152</v>
       </c>
       <c r="P25">
-        <v>73.80413416000002</v>
+        <v>73.09996608000002</v>
       </c>
       <c r="Q25">
-        <v>118.50413416</v>
+        <v>117.79996608</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09675640609457248</v>
+        <v>0.09731865265856424</v>
       </c>
       <c r="T25">
-        <v>0.7882793962039257</v>
+        <v>0.7969771717330434</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.556973667793732</v>
+        <v>5.325433098302327</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08457977602050883</v>
+        <v>0.08448191934819681</v>
       </c>
       <c r="C26">
-        <v>1340.275490152399</v>
+        <v>1328.670708130075</v>
       </c>
       <c r="D26">
-        <v>1704.583490152399</v>
+        <v>1708.895708130075</v>
       </c>
       <c r="E26">
-        <v>98.60799999999995</v>
+        <v>114.525</v>
       </c>
       <c r="F26">
-        <v>382.0079999999999</v>
+        <v>397.925</v>
       </c>
       <c r="G26">
         <v>17.7</v>
@@ -3413,28 +3413,28 @@
         <v>112.5</v>
       </c>
       <c r="M26">
-        <v>21.1250424</v>
+        <v>22.0052525</v>
       </c>
       <c r="N26">
-        <v>91.37495760000002</v>
+        <v>90.49474750000002</v>
       </c>
       <c r="O26">
-        <v>18.27499152</v>
+        <v>18.0989495</v>
       </c>
       <c r="P26">
-        <v>73.09996608000002</v>
+        <v>72.39579800000001</v>
       </c>
       <c r="Q26">
-        <v>117.79996608</v>
+        <v>117.095798</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09731865265856424</v>
+        <v>0.09789589246426242</v>
       </c>
       <c r="T26">
-        <v>0.7969771717330433</v>
+        <v>0.8059068879429373</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.325433098302327</v>
+        <v>5.112415774370234</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08448191934819681</v>
+        <v>0.08438406267588482</v>
       </c>
       <c r="C27">
-        <v>1328.670708130075</v>
+        <v>1317.087799351381</v>
       </c>
       <c r="D27">
-        <v>1708.895708130075</v>
+        <v>1713.229799351381</v>
       </c>
       <c r="E27">
-        <v>114.525</v>
+        <v>130.442</v>
       </c>
       <c r="F27">
-        <v>397.925</v>
+        <v>413.842</v>
       </c>
       <c r="G27">
         <v>17.7</v>
@@ -3495,28 +3495,28 @@
         <v>112.5</v>
       </c>
       <c r="M27">
-        <v>22.0052525</v>
+        <v>22.8854626</v>
       </c>
       <c r="N27">
-        <v>90.49474750000002</v>
+        <v>89.61453740000002</v>
       </c>
       <c r="O27">
-        <v>18.0989495</v>
+        <v>17.92290748</v>
       </c>
       <c r="P27">
-        <v>72.39579800000001</v>
+        <v>71.69162992000001</v>
       </c>
       <c r="Q27">
-        <v>117.095798</v>
+        <v>116.39162992</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09789589246426242</v>
+        <v>0.09848873334579031</v>
       </c>
       <c r="T27">
-        <v>0.8059068879429373</v>
+        <v>0.8150779478341799</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.112415774370234</v>
+        <v>4.915784398432917</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08438406267588482</v>
+        <v>0.08428620600357285</v>
       </c>
       <c r="C28">
-        <v>1317.087799351381</v>
+        <v>1305.526930663848</v>
       </c>
       <c r="D28">
-        <v>1713.229799351381</v>
+        <v>1717.585930663848</v>
       </c>
       <c r="E28">
-        <v>130.442</v>
+        <v>146.359</v>
       </c>
       <c r="F28">
-        <v>413.842</v>
+        <v>429.759</v>
       </c>
       <c r="G28">
         <v>17.7</v>
@@ -3577,28 +3577,28 @@
         <v>112.5</v>
       </c>
       <c r="M28">
-        <v>22.8854626</v>
+        <v>23.7656727</v>
       </c>
       <c r="N28">
-        <v>89.61453740000002</v>
+        <v>88.73432730000002</v>
       </c>
       <c r="O28">
-        <v>17.92290748</v>
+        <v>17.74686546000001</v>
       </c>
       <c r="P28">
-        <v>71.69162992000001</v>
+        <v>70.98746184000001</v>
       </c>
       <c r="Q28">
-        <v>116.39162992</v>
+        <v>115.68746184</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09848873334579031</v>
+        <v>0.09909781644325047</v>
       </c>
       <c r="T28">
-        <v>0.8150779478341799</v>
+        <v>0.824500269640251</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.915784398432917</v>
+        <v>4.733718309602068</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08428620600357285</v>
+        <v>0.08418834933126083</v>
       </c>
       <c r="C29">
-        <v>1305.526930663848</v>
+        <v>1293.988270616273</v>
       </c>
       <c r="D29">
-        <v>1717.585930663848</v>
+        <v>1721.964270616273</v>
       </c>
       <c r="E29">
-        <v>146.359</v>
+        <v>162.276</v>
       </c>
       <c r="F29">
-        <v>429.759</v>
+        <v>445.676</v>
       </c>
       <c r="G29">
         <v>17.7</v>
@@ -3659,28 +3659,28 @@
         <v>112.5</v>
       </c>
       <c r="M29">
-        <v>23.7656727</v>
+        <v>24.6458828</v>
       </c>
       <c r="N29">
-        <v>88.73432730000002</v>
+        <v>87.85411720000002</v>
       </c>
       <c r="O29">
-        <v>17.74686546000001</v>
+        <v>17.57082344000001</v>
       </c>
       <c r="P29">
-        <v>70.98746184000001</v>
+        <v>70.28329376000002</v>
       </c>
       <c r="Q29">
-        <v>115.68746184</v>
+        <v>114.98329376</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09909781644325047</v>
+        <v>0.09972381851564005</v>
       </c>
       <c r="T29">
-        <v>0.824500269640251</v>
+        <v>0.8341843226076018</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.733718309602068</v>
+        <v>4.564656941401994</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08418834933126083</v>
+        <v>0.08467049265894885</v>
       </c>
       <c r="C30">
-        <v>1293.988270616273</v>
+        <v>1256.712303265915</v>
       </c>
       <c r="D30">
-        <v>1721.964270616273</v>
+        <v>1700.605303265915</v>
       </c>
       <c r="E30">
-        <v>162.276</v>
+        <v>178.193</v>
       </c>
       <c r="F30">
-        <v>445.676</v>
+        <v>461.593</v>
       </c>
       <c r="G30">
         <v>17.7</v>
@@ -3741,45 +3741,45 @@
         <v>112.5</v>
       </c>
       <c r="M30">
-        <v>24.6458828</v>
+        <v>26.6800754</v>
       </c>
       <c r="N30">
-        <v>87.85411720000002</v>
+        <v>85.81992460000001</v>
       </c>
       <c r="O30">
-        <v>17.57082344000001</v>
+        <v>17.16398492</v>
       </c>
       <c r="P30">
-        <v>70.28329376000002</v>
+        <v>68.65593968</v>
       </c>
       <c r="Q30">
-        <v>114.98329376</v>
+        <v>113.35593968</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09972381851564005</v>
+        <v>0.1003674544492237</v>
       </c>
       <c r="T30">
-        <v>0.8341843226076018</v>
+        <v>0.844141165799385</v>
       </c>
       <c r="U30">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V30">
         <v>0.2</v>
       </c>
       <c r="W30">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.564656941401994</v>
+        <v>4.216629762598047</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08467049265894885</v>
+        <v>0.08459263598663685</v>
       </c>
       <c r="C31">
-        <v>1256.712303265915</v>
+        <v>1244.208411616532</v>
       </c>
       <c r="D31">
-        <v>1700.605303265915</v>
+        <v>1704.018411616532</v>
       </c>
       <c r="E31">
-        <v>178.1929999999999</v>
+        <v>194.11</v>
       </c>
       <c r="F31">
-        <v>461.5929999999999</v>
+        <v>477.5099999999999</v>
       </c>
       <c r="G31">
         <v>17.7</v>
@@ -3823,28 +3823,28 @@
         <v>112.5</v>
       </c>
       <c r="M31">
-        <v>26.6800754</v>
+        <v>27.600078</v>
       </c>
       <c r="N31">
-        <v>85.81992460000002</v>
+        <v>84.89992200000002</v>
       </c>
       <c r="O31">
-        <v>17.16398492</v>
+        <v>16.9799844</v>
       </c>
       <c r="P31">
-        <v>68.65593968000002</v>
+        <v>67.91993760000001</v>
       </c>
       <c r="Q31">
-        <v>113.35593968</v>
+        <v>112.6199376</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1003674544492237</v>
+        <v>0.1010294799809098</v>
       </c>
       <c r="T31">
-        <v>0.844141165799385</v>
+        <v>0.8543824902252194</v>
       </c>
       <c r="U31">
         <v>0.0578</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.216629762598048</v>
+        <v>4.076075437178114</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08459263598663685</v>
+        <v>0.08538277931432485</v>
       </c>
       <c r="C32">
-        <v>1244.208411616532</v>
+        <v>1194.27614534368</v>
       </c>
       <c r="D32">
-        <v>1704.018411616532</v>
+        <v>1670.00314534368</v>
       </c>
       <c r="E32">
-        <v>194.11</v>
+        <v>210.027</v>
       </c>
       <c r="F32">
-        <v>477.5099999999999</v>
+        <v>493.427</v>
       </c>
       <c r="G32">
         <v>17.7</v>
@@ -3905,45 +3905,45 @@
         <v>112.5</v>
       </c>
       <c r="M32">
-        <v>27.600078</v>
+        <v>30.2470751</v>
       </c>
       <c r="N32">
-        <v>84.89992200000002</v>
+        <v>82.25292490000001</v>
       </c>
       <c r="O32">
-        <v>16.9799844</v>
+        <v>16.45058498</v>
       </c>
       <c r="P32">
-        <v>67.91993760000001</v>
+        <v>65.80233992000001</v>
       </c>
       <c r="Q32">
-        <v>112.6199376</v>
+        <v>110.50233992</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1010294799809098</v>
+        <v>0.1017106946584418</v>
       </c>
       <c r="T32">
-        <v>0.8543824902252194</v>
+        <v>0.864920664634411</v>
       </c>
       <c r="U32">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V32">
         <v>0.2</v>
       </c>
       <c r="W32">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.076075437178114</v>
+        <v>3.719367893525679</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08538277931432485</v>
+        <v>0.08533292264201287</v>
       </c>
       <c r="C33">
-        <v>1194.27614534368</v>
+        <v>1180.465258274701</v>
       </c>
       <c r="D33">
-        <v>1670.00314534368</v>
+        <v>1672.109258274701</v>
       </c>
       <c r="E33">
-        <v>210.027</v>
+        <v>225.944</v>
       </c>
       <c r="F33">
-        <v>493.427</v>
+        <v>509.3439999999999</v>
       </c>
       <c r="G33">
         <v>17.7</v>
@@ -3987,28 +3987,28 @@
         <v>112.5</v>
       </c>
       <c r="M33">
-        <v>30.2470751</v>
+        <v>31.2227872</v>
       </c>
       <c r="N33">
-        <v>82.25292490000001</v>
+        <v>81.27721280000002</v>
       </c>
       <c r="O33">
-        <v>16.45058498</v>
+        <v>16.25544256</v>
       </c>
       <c r="P33">
-        <v>65.80233992000001</v>
+        <v>65.02177024000001</v>
       </c>
       <c r="Q33">
-        <v>110.50233992</v>
+        <v>109.72177024</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1017106946584418</v>
+        <v>0.1024119450617836</v>
       </c>
       <c r="T33">
-        <v>0.864920664634411</v>
+        <v>0.8757687853497554</v>
       </c>
       <c r="U33">
         <v>0.0613</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.719367893525679</v>
+        <v>3.603137646853002</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08533292264201287</v>
+        <v>0.08602226596970088</v>
       </c>
       <c r="C34">
-        <v>1180.465258274701</v>
+        <v>1135.891062252346</v>
       </c>
       <c r="D34">
-        <v>1672.109258274701</v>
+        <v>1643.452062252346</v>
       </c>
       <c r="E34">
-        <v>225.944</v>
+        <v>241.861</v>
       </c>
       <c r="F34">
-        <v>509.3439999999999</v>
+        <v>525.261</v>
       </c>
       <c r="G34">
         <v>17.7</v>
@@ -4069,45 +4069,45 @@
         <v>112.5</v>
       </c>
       <c r="M34">
-        <v>31.2227872</v>
+        <v>33.6692301</v>
       </c>
       <c r="N34">
-        <v>81.27721280000002</v>
+        <v>78.83076990000001</v>
       </c>
       <c r="O34">
-        <v>16.25544256</v>
+        <v>15.76615398</v>
       </c>
       <c r="P34">
-        <v>65.02177024000001</v>
+        <v>63.06461592000001</v>
       </c>
       <c r="Q34">
-        <v>109.72177024</v>
+        <v>107.76461592</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1024119450617836</v>
+        <v>0.1031341283129864</v>
       </c>
       <c r="T34">
-        <v>0.8757687853497554</v>
+        <v>0.8869407305640654</v>
       </c>
       <c r="U34">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V34">
         <v>0.2</v>
       </c>
       <c r="W34">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>3.603137646853002</v>
+        <v>3.341329744275917</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08602226596970088</v>
+        <v>0.08599480929738887</v>
       </c>
       <c r="C35">
-        <v>1135.891062252346</v>
+        <v>1121.096687922737</v>
       </c>
       <c r="D35">
-        <v>1643.452062252346</v>
+        <v>1644.574687922737</v>
       </c>
       <c r="E35">
-        <v>241.861</v>
+        <v>257.778</v>
       </c>
       <c r="F35">
-        <v>525.261</v>
+        <v>541.178</v>
       </c>
       <c r="G35">
         <v>17.7</v>
@@ -4151,28 +4151,28 @@
         <v>112.5</v>
       </c>
       <c r="M35">
-        <v>33.6692301</v>
+        <v>34.6895098</v>
       </c>
       <c r="N35">
-        <v>78.83076990000001</v>
+        <v>77.8104902</v>
       </c>
       <c r="O35">
-        <v>15.76615398</v>
+        <v>15.56209804</v>
       </c>
       <c r="P35">
-        <v>63.06461592000001</v>
+        <v>62.24839216</v>
       </c>
       <c r="Q35">
-        <v>107.76461592</v>
+        <v>106.94839216</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1031341283129864</v>
+        <v>0.1038781959051347</v>
       </c>
       <c r="T35">
-        <v>0.8869407305640654</v>
+        <v>0.8984512195727483</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.341329744275917</v>
+        <v>3.243055340032508</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08599480929738887</v>
+        <v>0.08596735262507688</v>
       </c>
       <c r="C36">
-        <v>1121.096687922737</v>
+        <v>1106.303848350246</v>
       </c>
       <c r="D36">
-        <v>1644.574687922737</v>
+        <v>1645.698848350246</v>
       </c>
       <c r="E36">
-        <v>257.778</v>
+        <v>273.6950000000001</v>
       </c>
       <c r="F36">
-        <v>541.178</v>
+        <v>557.095</v>
       </c>
       <c r="G36">
         <v>17.7</v>
@@ -4233,28 +4233,28 @@
         <v>112.5</v>
       </c>
       <c r="M36">
-        <v>34.6895098</v>
+        <v>35.70978950000001</v>
       </c>
       <c r="N36">
-        <v>77.8104902</v>
+        <v>76.7902105</v>
       </c>
       <c r="O36">
-        <v>15.56209804</v>
+        <v>15.3580421</v>
       </c>
       <c r="P36">
-        <v>62.24839216</v>
+        <v>61.4321684</v>
       </c>
       <c r="Q36">
-        <v>106.94839216</v>
+        <v>106.1321684</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1038781959051347</v>
+        <v>0.1046451578847337</v>
       </c>
       <c r="T36">
-        <v>0.8984512195727483</v>
+        <v>0.9103158774740061</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.243055340032508</v>
+        <v>3.150396616031578</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08596735262507688</v>
+        <v>0.08593989595276488</v>
       </c>
       <c r="C37">
-        <v>1106.303848350246</v>
+        <v>1091.512546684306</v>
       </c>
       <c r="D37">
-        <v>1645.698848350246</v>
+        <v>1646.824546684306</v>
       </c>
       <c r="E37">
-        <v>273.6950000000001</v>
+        <v>289.6120000000001</v>
       </c>
       <c r="F37">
-        <v>557.095</v>
+        <v>573.0120000000001</v>
       </c>
       <c r="G37">
         <v>17.7</v>
@@ -4315,28 +4315,28 @@
         <v>112.5</v>
       </c>
       <c r="M37">
-        <v>35.70978950000001</v>
+        <v>36.7300692</v>
       </c>
       <c r="N37">
-        <v>76.7902105</v>
+        <v>75.76993080000001</v>
       </c>
       <c r="O37">
-        <v>15.3580421</v>
+        <v>15.15398616</v>
       </c>
       <c r="P37">
-        <v>61.4321684</v>
+        <v>60.61594464000001</v>
       </c>
       <c r="Q37">
-        <v>106.1321684</v>
+        <v>105.31594464</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1046451578847337</v>
+        <v>0.1054360874261951</v>
       </c>
       <c r="T37">
-        <v>0.9103158774740061</v>
+        <v>0.9225513059346784</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.150396616031578</v>
+        <v>3.06288559891959</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0859398959527649</v>
+        <v>0.0882212392804529</v>
       </c>
       <c r="C38">
-        <v>1091.512546684306</v>
+        <v>987.0320757632138</v>
       </c>
       <c r="D38">
-        <v>1646.824546684306</v>
+        <v>1558.261075763214</v>
       </c>
       <c r="E38">
-        <v>289.612</v>
+        <v>305.529</v>
       </c>
       <c r="F38">
-        <v>573.0119999999999</v>
+        <v>588.929</v>
       </c>
       <c r="G38">
         <v>17.7</v>
@@ -4397,45 +4397,45 @@
         <v>112.5</v>
       </c>
       <c r="M38">
-        <v>36.7300692</v>
+        <v>42.3439951</v>
       </c>
       <c r="N38">
-        <v>75.76993080000003</v>
+        <v>70.15600490000001</v>
       </c>
       <c r="O38">
-        <v>15.15398616000001</v>
+        <v>14.03120098</v>
       </c>
       <c r="P38">
-        <v>60.61594464000002</v>
+        <v>56.12480392000001</v>
       </c>
       <c r="Q38">
-        <v>105.31594464</v>
+        <v>100.82480392</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1054360874261951</v>
+        <v>0.1062521258419887</v>
       </c>
       <c r="T38">
-        <v>0.9225513059346783</v>
+        <v>0.9351751606956893</v>
       </c>
       <c r="U38">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V38">
         <v>0.2</v>
       </c>
       <c r="W38">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.062885598919591</v>
+        <v>2.656811189740574</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0882212392804529</v>
+        <v>0.08825618260814092</v>
       </c>
       <c r="C39">
-        <v>987.0320757632138</v>
+        <v>969.8325575515217</v>
       </c>
       <c r="D39">
-        <v>1558.261075763214</v>
+        <v>1556.978557551522</v>
       </c>
       <c r="E39">
-        <v>305.529</v>
+        <v>321.4459999999999</v>
       </c>
       <c r="F39">
-        <v>588.929</v>
+        <v>604.8459999999999</v>
       </c>
       <c r="G39">
         <v>17.7</v>
@@ -4479,28 +4479,28 @@
         <v>112.5</v>
       </c>
       <c r="M39">
-        <v>42.3439951</v>
+        <v>43.48842739999999</v>
       </c>
       <c r="N39">
-        <v>70.15600490000001</v>
+        <v>69.01157260000002</v>
       </c>
       <c r="O39">
-        <v>14.03120098</v>
+        <v>13.80231452</v>
       </c>
       <c r="P39">
-        <v>56.12480392000001</v>
+        <v>55.20925808000002</v>
       </c>
       <c r="Q39">
-        <v>100.82480392</v>
+        <v>99.90925808000003</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1062521258419887</v>
+        <v>0.1070944880776466</v>
       </c>
       <c r="T39">
-        <v>0.9351751606956893</v>
+        <v>0.9482062365780229</v>
       </c>
       <c r="U39">
         <v>0.07190000000000001</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.656811189740574</v>
+        <v>2.586895105800032</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08825618260814092</v>
+        <v>0.08829112593582891</v>
       </c>
       <c r="C40">
-        <v>969.8325575515217</v>
+        <v>952.6351487428244</v>
       </c>
       <c r="D40">
-        <v>1556.978557551522</v>
+        <v>1555.698148742824</v>
       </c>
       <c r="E40">
-        <v>321.4459999999999</v>
+        <v>337.3629999999999</v>
       </c>
       <c r="F40">
-        <v>604.8459999999999</v>
+        <v>620.7629999999999</v>
       </c>
       <c r="G40">
         <v>17.7</v>
@@ -4561,28 +4561,28 @@
         <v>112.5</v>
       </c>
       <c r="M40">
-        <v>43.48842739999999</v>
+        <v>44.6328597</v>
       </c>
       <c r="N40">
-        <v>69.01157260000002</v>
+        <v>67.86714030000002</v>
       </c>
       <c r="O40">
-        <v>13.80231452</v>
+        <v>13.57342806</v>
       </c>
       <c r="P40">
-        <v>55.20925808000002</v>
+        <v>54.29371224000001</v>
       </c>
       <c r="Q40">
-        <v>99.90925808000003</v>
+        <v>98.99371224000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1070944880776466</v>
+        <v>0.1079644687472605</v>
       </c>
       <c r="T40">
-        <v>0.9482062365780229</v>
+        <v>0.9616645608499417</v>
       </c>
       <c r="U40">
         <v>0.07190000000000001</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.586895105800032</v>
+        <v>2.52056446206157</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08829112593582891</v>
+        <v>0.08957406926351692</v>
       </c>
       <c r="C41">
-        <v>952.6351487428244</v>
+        <v>891.1232887399495</v>
       </c>
       <c r="D41">
-        <v>1555.698148742824</v>
+        <v>1510.103288739949</v>
       </c>
       <c r="E41">
-        <v>337.3629999999999</v>
+        <v>353.28</v>
       </c>
       <c r="F41">
-        <v>620.7629999999999</v>
+        <v>636.6799999999999</v>
       </c>
       <c r="G41">
         <v>17.7</v>
@@ -4643,45 +4643,45 @@
         <v>112.5</v>
       </c>
       <c r="M41">
-        <v>44.6328597</v>
+        <v>48.260344</v>
       </c>
       <c r="N41">
-        <v>67.86714030000002</v>
+        <v>64.23965600000001</v>
       </c>
       <c r="O41">
-        <v>13.57342806</v>
+        <v>12.8479312</v>
       </c>
       <c r="P41">
-        <v>54.29371224000001</v>
+        <v>51.39172480000001</v>
       </c>
       <c r="Q41">
-        <v>98.99371224000001</v>
+        <v>96.09172480000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1079644687472605</v>
+        <v>0.1088634487725282</v>
       </c>
       <c r="T41">
-        <v>0.9616645608499417</v>
+        <v>0.9755714959309242</v>
       </c>
       <c r="U41">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V41">
         <v>0.2</v>
       </c>
       <c r="W41">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.52056446206157</v>
+        <v>2.331106467040517</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08957406926351692</v>
+        <v>0.08964021259120494</v>
       </c>
       <c r="C42">
-        <v>891.1232887399495</v>
+        <v>872.9279408313466</v>
       </c>
       <c r="D42">
-        <v>1510.103288739949</v>
+        <v>1507.824940831347</v>
       </c>
       <c r="E42">
-        <v>353.28</v>
+        <v>369.197</v>
       </c>
       <c r="F42">
-        <v>636.6799999999999</v>
+        <v>652.597</v>
       </c>
       <c r="G42">
         <v>17.7</v>
@@ -4725,28 +4725,28 @@
         <v>112.5</v>
       </c>
       <c r="M42">
-        <v>48.260344</v>
+        <v>49.4668526</v>
       </c>
       <c r="N42">
-        <v>64.23965600000001</v>
+        <v>63.03314740000001</v>
       </c>
       <c r="O42">
-        <v>12.8479312</v>
+        <v>12.60662948</v>
       </c>
       <c r="P42">
-        <v>51.39172480000001</v>
+        <v>50.42651792000001</v>
       </c>
       <c r="Q42">
-        <v>96.09172480000001</v>
+        <v>95.12651792000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1088634487725282</v>
+        <v>0.1097929026969575</v>
       </c>
       <c r="T42">
-        <v>0.9755714959309242</v>
+        <v>0.9899498525400756</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.331106467040517</v>
+        <v>2.274250211746846</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08964021259120494</v>
+        <v>0.08970635591889295</v>
       </c>
       <c r="C43">
-        <v>872.9279408313466</v>
+        <v>854.7394574192002</v>
       </c>
       <c r="D43">
-        <v>1507.824940831347</v>
+        <v>1505.5534574192</v>
       </c>
       <c r="E43">
-        <v>369.197</v>
+        <v>385.114</v>
       </c>
       <c r="F43">
-        <v>652.597</v>
+        <v>668.514</v>
       </c>
       <c r="G43">
         <v>17.7</v>
@@ -4807,28 +4807,28 @@
         <v>112.5</v>
       </c>
       <c r="M43">
-        <v>49.4668526</v>
+        <v>50.6733612</v>
       </c>
       <c r="N43">
-        <v>63.03314740000001</v>
+        <v>61.82663880000001</v>
       </c>
       <c r="O43">
-        <v>12.60662948</v>
+        <v>12.36532776</v>
       </c>
       <c r="P43">
-        <v>50.42651792000001</v>
+        <v>49.46131104000001</v>
       </c>
       <c r="Q43">
-        <v>95.12651792000001</v>
+        <v>94.16131104000002</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1097929026969575</v>
+        <v>0.110754406756712</v>
       </c>
       <c r="T43">
-        <v>0.9899498525400756</v>
+        <v>1.004824014549543</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.274250211746846</v>
+        <v>2.220101397181445</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08970635591889294</v>
+        <v>0.08977249924658096</v>
       </c>
       <c r="C44">
-        <v>854.7394574192008</v>
+        <v>836.557807526833</v>
       </c>
       <c r="D44">
-        <v>1505.553457419201</v>
+        <v>1503.288807526833</v>
       </c>
       <c r="E44">
-        <v>385.1139999999999</v>
+        <v>401.0309999999999</v>
       </c>
       <c r="F44">
-        <v>668.5139999999999</v>
+        <v>684.4309999999999</v>
       </c>
       <c r="G44">
         <v>17.7</v>
@@ -4889,28 +4889,28 @@
         <v>112.5</v>
       </c>
       <c r="M44">
-        <v>50.6733612</v>
+        <v>51.8798698</v>
       </c>
       <c r="N44">
-        <v>61.82663880000002</v>
+        <v>60.62013020000001</v>
       </c>
       <c r="O44">
-        <v>12.36532776</v>
+        <v>12.12402604</v>
       </c>
       <c r="P44">
-        <v>49.46131104000001</v>
+        <v>48.49610416000001</v>
       </c>
       <c r="Q44">
-        <v>94.16131104000002</v>
+        <v>93.19610416</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1107544067567119</v>
+        <v>0.1117496478010192</v>
       </c>
       <c r="T44">
-        <v>1.004824014549542</v>
+        <v>1.020220076980394</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.220101397181445</v>
+        <v>2.168471132130714</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08977249924658096</v>
+        <v>0.08983864257426896</v>
       </c>
       <c r="C45">
-        <v>836.557807526833</v>
+        <v>818.3829603636677</v>
       </c>
       <c r="D45">
-        <v>1503.288807526833</v>
+        <v>1501.030960363668</v>
       </c>
       <c r="E45">
-        <v>401.0309999999999</v>
+        <v>416.948</v>
       </c>
       <c r="F45">
-        <v>684.4309999999999</v>
+        <v>700.348</v>
       </c>
       <c r="G45">
         <v>17.7</v>
@@ -4971,28 +4971,28 @@
         <v>112.5</v>
       </c>
       <c r="M45">
-        <v>51.8798698</v>
+        <v>53.0863784</v>
       </c>
       <c r="N45">
-        <v>60.62013020000001</v>
+        <v>59.41362160000001</v>
       </c>
       <c r="O45">
-        <v>12.12402604</v>
+        <v>11.88272432</v>
       </c>
       <c r="P45">
-        <v>48.49610416000001</v>
+        <v>47.53089728000001</v>
       </c>
       <c r="Q45">
-        <v>93.19610416</v>
+        <v>92.23089728000002</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1117496478010192</v>
+        <v>0.1127804331683374</v>
       </c>
       <c r="T45">
-        <v>1.020220076980394</v>
+        <v>1.036165998783777</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.168471132130714</v>
+        <v>2.119187697309561</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08983864257426896</v>
+        <v>0.08990478590195697</v>
       </c>
       <c r="C46">
-        <v>818.3829603636677</v>
+        <v>800.2148853238324</v>
       </c>
       <c r="D46">
-        <v>1501.030960363668</v>
+        <v>1498.779885323832</v>
       </c>
       <c r="E46">
-        <v>416.948</v>
+        <v>432.865</v>
       </c>
       <c r="F46">
-        <v>700.348</v>
+        <v>716.265</v>
       </c>
       <c r="G46">
         <v>17.7</v>
@@ -5053,28 +5053,28 @@
         <v>112.5</v>
       </c>
       <c r="M46">
-        <v>53.0863784</v>
+        <v>54.292887</v>
       </c>
       <c r="N46">
-        <v>59.41362160000001</v>
+        <v>58.20711300000001</v>
       </c>
       <c r="O46">
-        <v>11.88272432</v>
+        <v>11.6414226</v>
       </c>
       <c r="P46">
-        <v>47.53089728000001</v>
+        <v>46.56569040000001</v>
       </c>
       <c r="Q46">
-        <v>92.23089728000002</v>
+        <v>91.26569040000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1127804331683374</v>
+        <v>0.1138487016399218</v>
       </c>
       <c r="T46">
-        <v>1.036165998783777</v>
+        <v>1.0526917722891</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.119187697309561</v>
+        <v>2.072094637369348</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08990478590195697</v>
+        <v>0.08997092922964497</v>
       </c>
       <c r="C47">
-        <v>800.2148853238324</v>
+        <v>782.0535519847768</v>
       </c>
       <c r="D47">
-        <v>1498.779885323832</v>
+        <v>1496.535551984777</v>
       </c>
       <c r="E47">
-        <v>432.865</v>
+        <v>448.7819999999999</v>
       </c>
       <c r="F47">
-        <v>716.265</v>
+        <v>732.1819999999999</v>
       </c>
       <c r="G47">
         <v>17.7</v>
@@ -5135,28 +5135,28 @@
         <v>112.5</v>
       </c>
       <c r="M47">
-        <v>54.292887</v>
+        <v>55.4993956</v>
       </c>
       <c r="N47">
-        <v>58.20711300000001</v>
+        <v>57.00060440000001</v>
       </c>
       <c r="O47">
-        <v>11.6414226</v>
+        <v>11.40012088</v>
       </c>
       <c r="P47">
-        <v>46.56569040000001</v>
+        <v>45.60048352000001</v>
       </c>
       <c r="Q47">
-        <v>91.26569040000001</v>
+        <v>90.30048352000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1138487016399218</v>
+        <v>0.1149565356104536</v>
       </c>
       <c r="T47">
-        <v>1.0526917722891</v>
+        <v>1.069829611479806</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.072094637369348</v>
+        <v>2.027049101774363</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08997092922964497</v>
+        <v>0.09537627255733297</v>
       </c>
       <c r="C48">
-        <v>782.0535519847768</v>
+        <v>602.9680029331341</v>
       </c>
       <c r="D48">
-        <v>1496.535551984777</v>
+        <v>1333.367002933134</v>
       </c>
       <c r="E48">
-        <v>448.7819999999999</v>
+        <v>464.699</v>
       </c>
       <c r="F48">
-        <v>732.1819999999999</v>
+        <v>748.0989999999999</v>
       </c>
       <c r="G48">
         <v>17.7</v>
@@ -5217,45 +5217,45 @@
         <v>112.5</v>
       </c>
       <c r="M48">
-        <v>55.4993956</v>
+        <v>67.32890999999999</v>
       </c>
       <c r="N48">
-        <v>57.00060440000001</v>
+        <v>45.17109000000002</v>
       </c>
       <c r="O48">
-        <v>11.40012088</v>
+        <v>9.034218000000005</v>
       </c>
       <c r="P48">
-        <v>45.60048352000001</v>
+        <v>36.13687200000002</v>
       </c>
       <c r="Q48">
-        <v>90.30048352000001</v>
+        <v>80.83687200000003</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1149565356104536</v>
+        <v>0.1161061746364773</v>
       </c>
       <c r="T48">
-        <v>1.069829611479806</v>
+        <v>1.087614161583368</v>
       </c>
       <c r="U48">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V48">
         <v>0.2</v>
       </c>
       <c r="W48">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.027049101774363</v>
+        <v>1.670901845878688</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09537627255733297</v>
+        <v>0.095556015885021</v>
       </c>
       <c r="C49">
-        <v>602.9680029331341</v>
+        <v>582.2342221303776</v>
       </c>
       <c r="D49">
-        <v>1333.367002933134</v>
+        <v>1328.550222130378</v>
       </c>
       <c r="E49">
-        <v>464.699</v>
+        <v>480.616</v>
       </c>
       <c r="F49">
-        <v>748.0989999999999</v>
+        <v>764.016</v>
       </c>
       <c r="G49">
         <v>17.7</v>
@@ -5299,28 +5299,28 @@
         <v>112.5</v>
       </c>
       <c r="M49">
-        <v>67.32890999999999</v>
+        <v>68.76143999999999</v>
       </c>
       <c r="N49">
-        <v>45.17109000000002</v>
+        <v>43.73856000000002</v>
       </c>
       <c r="O49">
-        <v>9.034218000000005</v>
+        <v>8.747712000000005</v>
       </c>
       <c r="P49">
-        <v>36.13687200000002</v>
+        <v>34.99084800000001</v>
       </c>
       <c r="Q49">
-        <v>80.83687200000003</v>
+        <v>79.69084800000002</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1161061746364773</v>
+        <v>0.1173000305481173</v>
       </c>
       <c r="T49">
-        <v>1.087614161583368</v>
+        <v>1.10608273284476</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.670901845878688</v>
+        <v>1.636091390756215</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09555601588502098</v>
+        <v>0.09573575921270898</v>
       </c>
       <c r="C50">
-        <v>582.2342221303784</v>
+        <v>561.5351172482007</v>
       </c>
       <c r="D50">
-        <v>1328.550222130378</v>
+        <v>1323.7681172482</v>
       </c>
       <c r="E50">
-        <v>480.6159999999999</v>
+        <v>496.5329999999999</v>
       </c>
       <c r="F50">
-        <v>764.0159999999998</v>
+        <v>779.9329999999999</v>
       </c>
       <c r="G50">
         <v>17.7</v>
@@ -5381,28 +5381,28 @@
         <v>112.5</v>
       </c>
       <c r="M50">
-        <v>68.76143999999998</v>
+        <v>70.19396999999999</v>
       </c>
       <c r="N50">
-        <v>43.73856000000004</v>
+        <v>42.30603000000002</v>
       </c>
       <c r="O50">
-        <v>8.747712000000007</v>
+        <v>8.461206000000004</v>
       </c>
       <c r="P50">
-        <v>34.99084800000003</v>
+        <v>33.84482400000002</v>
       </c>
       <c r="Q50">
-        <v>79.69084800000003</v>
+        <v>78.54482400000002</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1173000305481173</v>
+        <v>0.1185407043386451</v>
       </c>
       <c r="T50">
-        <v>1.10608273284476</v>
+        <v>1.125275561802677</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.636091390756215</v>
+        <v>1.6027017705367</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09573575921270898</v>
+        <v>0.09591550254039699</v>
       </c>
       <c r="C51">
-        <v>561.5351172482007</v>
+        <v>540.8703151825684</v>
       </c>
       <c r="D51">
-        <v>1323.7681172482</v>
+        <v>1319.020315182568</v>
       </c>
       <c r="E51">
-        <v>496.5329999999999</v>
+        <v>512.4499999999999</v>
       </c>
       <c r="F51">
-        <v>779.9329999999999</v>
+        <v>795.8499999999999</v>
       </c>
       <c r="G51">
         <v>17.7</v>
@@ -5463,28 +5463,28 @@
         <v>112.5</v>
       </c>
       <c r="M51">
-        <v>70.19396999999999</v>
+        <v>71.62649999999999</v>
       </c>
       <c r="N51">
-        <v>42.30603000000002</v>
+        <v>40.87350000000002</v>
       </c>
       <c r="O51">
-        <v>8.461206000000004</v>
+        <v>8.174700000000005</v>
       </c>
       <c r="P51">
-        <v>33.84482400000002</v>
+        <v>32.69880000000002</v>
       </c>
       <c r="Q51">
-        <v>78.54482400000002</v>
+        <v>77.39880000000002</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1185407043386451</v>
+        <v>0.119831005080794</v>
       </c>
       <c r="T51">
-        <v>1.125275561802677</v>
+        <v>1.145236103918911</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.6027017705367</v>
+        <v>1.570647735125966</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09591550254039699</v>
+        <v>0.09609524586808499</v>
       </c>
       <c r="C52">
-        <v>540.8703151825684</v>
+        <v>520.2394481629934</v>
       </c>
       <c r="D52">
-        <v>1319.020315182568</v>
+        <v>1314.306448162993</v>
       </c>
       <c r="E52">
-        <v>512.4499999999999</v>
+        <v>528.367</v>
       </c>
       <c r="F52">
-        <v>795.8499999999999</v>
+        <v>811.7669999999999</v>
       </c>
       <c r="G52">
         <v>17.7</v>
@@ -5545,28 +5545,28 @@
         <v>112.5</v>
       </c>
       <c r="M52">
-        <v>71.62649999999999</v>
+        <v>73.05902999999999</v>
       </c>
       <c r="N52">
-        <v>40.87350000000002</v>
+        <v>39.44097000000002</v>
       </c>
       <c r="O52">
-        <v>8.174700000000005</v>
+        <v>7.888194000000005</v>
       </c>
       <c r="P52">
-        <v>32.69880000000002</v>
+        <v>31.55277600000002</v>
       </c>
       <c r="Q52">
-        <v>77.39880000000002</v>
+        <v>76.25277600000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.119831005080794</v>
+        <v>0.1211739711593571</v>
       </c>
       <c r="T52">
-        <v>1.145236103918911</v>
+        <v>1.166011362039889</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.570647735125966</v>
+        <v>1.539850720711732</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09609524586808499</v>
+        <v>0.09627498919577301</v>
       </c>
       <c r="C53">
-        <v>520.2394481629934</v>
+        <v>499.6421536575629</v>
       </c>
       <c r="D53">
-        <v>1314.306448162993</v>
+        <v>1309.626153657563</v>
       </c>
       <c r="E53">
-        <v>528.367</v>
+        <v>544.284</v>
       </c>
       <c r="F53">
-        <v>811.7669999999999</v>
+        <v>827.684</v>
       </c>
       <c r="G53">
         <v>17.7</v>
@@ -5627,28 +5627,28 @@
         <v>112.5</v>
       </c>
       <c r="M53">
-        <v>73.05902999999999</v>
+        <v>74.49155999999999</v>
       </c>
       <c r="N53">
-        <v>39.44097000000002</v>
+        <v>38.00844000000002</v>
       </c>
       <c r="O53">
-        <v>7.888194000000005</v>
+        <v>7.601688000000005</v>
       </c>
       <c r="P53">
-        <v>31.55277600000002</v>
+        <v>30.40675200000002</v>
       </c>
       <c r="Q53">
-        <v>76.25277600000001</v>
+        <v>75.10675200000003</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1211739711593571</v>
+        <v>0.1225728941578604</v>
       </c>
       <c r="T53">
-        <v>1.166011362039889</v>
+        <v>1.187652255915908</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.539850720711732</v>
+        <v>1.510238206851891</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09627498919577301</v>
+        <v>0.1223621308430221</v>
       </c>
       <c r="C54">
-        <v>499.6421536575629</v>
+        <v>37.49406526929351</v>
       </c>
       <c r="D54">
-        <v>1309.626153657563</v>
+        <v>863.3950652692935</v>
       </c>
       <c r="E54">
-        <v>544.284</v>
+        <v>560.201</v>
       </c>
       <c r="F54">
-        <v>827.684</v>
+        <v>843.601</v>
       </c>
       <c r="G54">
         <v>17.7</v>
@@ -5709,45 +5709,45 @@
         <v>112.5</v>
       </c>
       <c r="M54">
-        <v>74.49155999999999</v>
+        <v>123.8406268</v>
       </c>
       <c r="N54">
-        <v>38.00844000000002</v>
+        <v>-11.3406268</v>
       </c>
       <c r="O54">
-        <v>7.601688000000005</v>
+        <v>-2.268125359999999</v>
       </c>
       <c r="P54">
-        <v>30.40675200000002</v>
+        <v>-9.072501439999996</v>
       </c>
       <c r="Q54">
-        <v>75.10675200000003</v>
+        <v>35.62749856000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1225728941578604</v>
+        <v>0.124880766934374</v>
       </c>
       <c r="T54">
-        <v>1.187652255915908</v>
+        <v>1.223354313777076</v>
       </c>
       <c r="U54">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.2</v>
+        <v>0.1816851269360662</v>
       </c>
       <c r="W54">
-        <v>0.07199999999999999</v>
+        <v>0.1201286233657855</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y54">
-        <v>1.510238206851891</v>
+        <v>0.908425634680331</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1223621308430221</v>
+        <v>0.1233721308430221</v>
       </c>
       <c r="C55">
-        <v>37.49406526929351</v>
+        <v>10.33554068507578</v>
       </c>
       <c r="D55">
-        <v>863.3950652692935</v>
+        <v>852.1535406850757</v>
       </c>
       <c r="E55">
-        <v>560.201</v>
+        <v>576.1179999999999</v>
       </c>
       <c r="F55">
-        <v>843.601</v>
+        <v>859.5179999999999</v>
       </c>
       <c r="G55">
         <v>17.7</v>
@@ -5791,37 +5791,37 @@
         <v>112.5</v>
       </c>
       <c r="M55">
-        <v>123.8406268</v>
+        <v>126.1772424</v>
       </c>
       <c r="N55">
-        <v>-11.3406268</v>
+        <v>-13.67724239999998</v>
       </c>
       <c r="O55">
-        <v>-2.268125359999999</v>
+        <v>-2.735448479999997</v>
       </c>
       <c r="P55">
-        <v>-9.072501439999996</v>
+        <v>-10.94179391999999</v>
       </c>
       <c r="Q55">
-        <v>35.62749856000001</v>
+        <v>33.75820608000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.124880766934374</v>
+        <v>0.126599914041643</v>
       </c>
       <c r="T55">
-        <v>1.223354313777076</v>
+        <v>1.249948972772229</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.1816851269360662</v>
+        <v>0.1783205875483613</v>
       </c>
       <c r="W55">
-        <v>0.1201286233657855</v>
+        <v>0.1206225377479006</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.908425634680331</v>
+        <v>0.8916029377418064</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1233721308430221</v>
+        <v>0.1243821308430221</v>
       </c>
       <c r="C56">
-        <v>10.33554068507578</v>
+        <v>-16.53401388246641</v>
       </c>
       <c r="D56">
-        <v>852.1535406850757</v>
+        <v>841.2009861175335</v>
       </c>
       <c r="E56">
-        <v>576.1179999999999</v>
+        <v>592.035</v>
       </c>
       <c r="F56">
-        <v>859.5179999999999</v>
+        <v>875.4349999999999</v>
       </c>
       <c r="G56">
         <v>17.7</v>
@@ -5873,37 +5873,37 @@
         <v>112.5</v>
       </c>
       <c r="M56">
-        <v>126.1772424</v>
+        <v>128.513858</v>
       </c>
       <c r="N56">
-        <v>-13.67724239999998</v>
+        <v>-16.01385799999998</v>
       </c>
       <c r="O56">
-        <v>-2.735448479999997</v>
+        <v>-3.202771599999997</v>
       </c>
       <c r="P56">
-        <v>-10.94179391999999</v>
+        <v>-12.81108639999999</v>
       </c>
       <c r="Q56">
-        <v>33.75820608000001</v>
+        <v>31.88891360000002</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.126599914041643</v>
+        <v>0.1283954676870128</v>
       </c>
       <c r="T56">
-        <v>1.249948972772229</v>
+        <v>1.277725616611613</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.1783205875483613</v>
+        <v>0.175078395047482</v>
       </c>
       <c r="W56">
-        <v>0.1206225377479006</v>
+        <v>0.1210984916070297</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8916029377418064</v>
+        <v>0.87539197523741</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1243821308430221</v>
+        <v>0.1253921308430221</v>
       </c>
       <c r="C57">
-        <v>-16.53401388246641</v>
+        <v>-43.12559925893254</v>
       </c>
       <c r="D57">
-        <v>841.2009861175335</v>
+        <v>830.5264007410674</v>
       </c>
       <c r="E57">
-        <v>592.035</v>
+        <v>607.952</v>
       </c>
       <c r="F57">
-        <v>875.4349999999999</v>
+        <v>891.352</v>
       </c>
       <c r="G57">
         <v>17.7</v>
@@ -5955,37 +5955,37 @@
         <v>112.5</v>
       </c>
       <c r="M57">
-        <v>128.513858</v>
+        <v>130.8504736</v>
       </c>
       <c r="N57">
-        <v>-16.01385799999998</v>
+        <v>-18.3504736</v>
       </c>
       <c r="O57">
-        <v>-3.202771599999997</v>
+        <v>-3.67009472</v>
       </c>
       <c r="P57">
-        <v>-12.81108639999999</v>
+        <v>-14.68037888</v>
       </c>
       <c r="Q57">
-        <v>31.88891360000002</v>
+        <v>30.01962112</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1283954676870128</v>
+        <v>0.1302726374071722</v>
       </c>
       <c r="T57">
-        <v>1.277725616611613</v>
+        <v>1.306764835170967</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.175078395047482</v>
+        <v>0.1719519951359198</v>
       </c>
       <c r="W57">
-        <v>0.1210984916070297</v>
+        <v>0.121557447114047</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.87539197523741</v>
+        <v>0.8597599756795989</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1253921308430221</v>
+        <v>0.1264021308430221</v>
       </c>
       <c r="C58">
-        <v>-43.12559925893254</v>
+        <v>-69.44966487835347</v>
       </c>
       <c r="D58">
-        <v>830.5264007410674</v>
+        <v>820.1193351216465</v>
       </c>
       <c r="E58">
-        <v>607.952</v>
+        <v>623.869</v>
       </c>
       <c r="F58">
-        <v>891.352</v>
+        <v>907.269</v>
       </c>
       <c r="G58">
         <v>17.7</v>
@@ -6037,37 +6037,37 @@
         <v>112.5</v>
       </c>
       <c r="M58">
-        <v>130.8504736</v>
+        <v>133.1870892</v>
       </c>
       <c r="N58">
-        <v>-18.3504736</v>
+        <v>-20.68708919999999</v>
       </c>
       <c r="O58">
-        <v>-3.67009472</v>
+        <v>-4.137417839999998</v>
       </c>
       <c r="P58">
-        <v>-14.68037888</v>
+        <v>-16.54967135999999</v>
       </c>
       <c r="Q58">
-        <v>30.01962112</v>
+        <v>28.15032864000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1302726374071722</v>
+        <v>0.1322371173468739</v>
       </c>
       <c r="T58">
-        <v>1.306764835170967</v>
+        <v>1.337154715058664</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.1719519951359198</v>
+        <v>0.1689352934668686</v>
       </c>
       <c r="W58">
-        <v>0.121557447114047</v>
+        <v>0.1220002989190637</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8597599756795989</v>
+        <v>0.8446764673343429</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1264021308430221</v>
+        <v>0.1274121308430221</v>
       </c>
       <c r="C59">
-        <v>-69.44966487835347</v>
+        <v>-95.51614290222858</v>
       </c>
       <c r="D59">
-        <v>820.1193351216465</v>
+        <v>809.9698570977714</v>
       </c>
       <c r="E59">
-        <v>623.869</v>
+        <v>639.7860000000001</v>
       </c>
       <c r="F59">
-        <v>907.269</v>
+        <v>923.186</v>
       </c>
       <c r="G59">
         <v>17.7</v>
@@ -6119,37 +6119,37 @@
         <v>112.5</v>
       </c>
       <c r="M59">
-        <v>133.1870892</v>
+        <v>135.5237048</v>
       </c>
       <c r="N59">
-        <v>-20.68708919999999</v>
+        <v>-23.0237048</v>
       </c>
       <c r="O59">
-        <v>-4.137417839999998</v>
+        <v>-4.604740960000001</v>
       </c>
       <c r="P59">
-        <v>-16.54967135999999</v>
+        <v>-18.41896384</v>
       </c>
       <c r="Q59">
-        <v>28.15032864000001</v>
+        <v>26.28103616</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1322371173468739</v>
+        <v>0.1342951439503709</v>
       </c>
       <c r="T59">
-        <v>1.337154715058664</v>
+        <v>1.368991732083871</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.1689352934668686</v>
+        <v>0.1660226159933019</v>
       </c>
       <c r="W59">
-        <v>0.1220002989190637</v>
+        <v>0.1224278799721833</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8446764673343429</v>
+        <v>0.8301130799665093</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1274121308430221</v>
+        <v>0.1284221308430221</v>
       </c>
       <c r="C60">
-        <v>-95.51614290222835</v>
+        <v>-121.3344798360704</v>
       </c>
       <c r="D60">
-        <v>809.9698570977714</v>
+        <v>800.0685201639294</v>
       </c>
       <c r="E60">
-        <v>639.7859999999998</v>
+        <v>655.7029999999999</v>
       </c>
       <c r="F60">
-        <v>923.1859999999998</v>
+        <v>939.1029999999998</v>
       </c>
       <c r="G60">
         <v>17.7</v>
@@ -6201,37 +6201,37 @@
         <v>112.5</v>
       </c>
       <c r="M60">
-        <v>135.5237048</v>
+        <v>137.8603204</v>
       </c>
       <c r="N60">
-        <v>-23.02370479999998</v>
+        <v>-25.36032039999996</v>
       </c>
       <c r="O60">
-        <v>-4.604740959999996</v>
+        <v>-5.072064079999993</v>
       </c>
       <c r="P60">
-        <v>-18.41896383999998</v>
+        <v>-20.28825631999997</v>
       </c>
       <c r="Q60">
-        <v>26.28103616000002</v>
+        <v>24.41174368000003</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1342951439503709</v>
+        <v>0.1364535620955019</v>
       </c>
       <c r="T60">
-        <v>1.36899173208387</v>
+        <v>1.402381774329818</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.1660226159933019</v>
+        <v>0.1632086733493476</v>
       </c>
       <c r="W60">
-        <v>0.1224278799721833</v>
+        <v>0.1228409667523158</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8301130799665095</v>
+        <v>0.8160433667467382</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1284221308430221</v>
+        <v>0.1294321308430221</v>
       </c>
       <c r="C61">
-        <v>-121.3344798360704</v>
+        <v>-146.9136658550098</v>
       </c>
       <c r="D61">
-        <v>800.0685201639294</v>
+        <v>790.4063341449901</v>
       </c>
       <c r="E61">
-        <v>655.7029999999999</v>
+        <v>671.6199999999999</v>
       </c>
       <c r="F61">
-        <v>939.1029999999998</v>
+        <v>955.0199999999999</v>
       </c>
       <c r="G61">
         <v>17.7</v>
@@ -6283,37 +6283,37 @@
         <v>112.5</v>
       </c>
       <c r="M61">
-        <v>137.8603204</v>
+        <v>140.196936</v>
       </c>
       <c r="N61">
-        <v>-25.36032039999996</v>
+        <v>-27.69693599999998</v>
       </c>
       <c r="O61">
-        <v>-5.072064079999993</v>
+        <v>-5.539387199999997</v>
       </c>
       <c r="P61">
-        <v>-20.28825631999997</v>
+        <v>-22.15754879999998</v>
       </c>
       <c r="Q61">
-        <v>24.41174368000003</v>
+        <v>22.54245120000002</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1364535620955019</v>
+        <v>0.1387199011478895</v>
       </c>
       <c r="T61">
-        <v>1.402381774329818</v>
+        <v>1.437441318688064</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.1632086733493476</v>
+        <v>0.1604885287935252</v>
       </c>
       <c r="W61">
-        <v>0.1228409667523158</v>
+        <v>0.1232402839731105</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8160433667467382</v>
+        <v>0.8024426439676258</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1294321308430221</v>
+        <v>0.1644471721160769</v>
       </c>
       <c r="C62">
-        <v>-146.9136658550098</v>
+        <v>-396.0946359856609</v>
       </c>
       <c r="D62">
-        <v>790.4063341449901</v>
+        <v>557.1423640143389</v>
       </c>
       <c r="E62">
-        <v>671.6199999999999</v>
+        <v>687.5369999999999</v>
       </c>
       <c r="F62">
-        <v>955.0199999999999</v>
+        <v>970.9369999999999</v>
       </c>
       <c r="G62">
         <v>17.7</v>
@@ -6365,45 +6365,45 @@
         <v>112.5</v>
       </c>
       <c r="M62">
-        <v>140.196936</v>
+        <v>194.9641496</v>
       </c>
       <c r="N62">
-        <v>-27.69693599999998</v>
+        <v>-82.46414959999997</v>
       </c>
       <c r="O62">
-        <v>-5.539387199999997</v>
+        <v>-16.49282991999999</v>
       </c>
       <c r="P62">
-        <v>-22.15754879999998</v>
+        <v>-65.97131967999998</v>
       </c>
       <c r="Q62">
-        <v>22.54245120000002</v>
+        <v>-21.27131967999998</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1387199011478895</v>
+        <v>0.143833337774899</v>
       </c>
       <c r="T62">
-        <v>1.437441318688064</v>
+        <v>1.516544557040179</v>
       </c>
       <c r="U62">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1604885287935252</v>
+        <v>0.1154058325397892</v>
       </c>
       <c r="W62">
-        <v>0.1232402839731105</v>
+        <v>0.1776265088260103</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.8024426439676258</v>
+        <v>0.5770291626989459</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1644471721160769</v>
+        <v>0.1659971721160769</v>
       </c>
       <c r="C63">
-        <v>-396.0946359856609</v>
+        <v>-419.1962531361231</v>
       </c>
       <c r="D63">
-        <v>557.1423640143389</v>
+        <v>549.9577468638768</v>
       </c>
       <c r="E63">
-        <v>687.5369999999999</v>
+        <v>703.454</v>
       </c>
       <c r="F63">
-        <v>970.9369999999999</v>
+        <v>986.8539999999999</v>
       </c>
       <c r="G63">
         <v>17.7</v>
@@ -6447,37 +6447,37 @@
         <v>112.5</v>
       </c>
       <c r="M63">
-        <v>194.9641496</v>
+        <v>198.1602832</v>
       </c>
       <c r="N63">
-        <v>-82.46414959999997</v>
+        <v>-85.66028319999997</v>
       </c>
       <c r="O63">
-        <v>-16.49282991999999</v>
+        <v>-17.13205663999999</v>
       </c>
       <c r="P63">
-        <v>-65.97131967999998</v>
+        <v>-68.52822655999998</v>
       </c>
       <c r="Q63">
-        <v>-21.27131967999998</v>
+        <v>-23.82822655999998</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.143833337774899</v>
+        <v>0.1464131624531858</v>
       </c>
       <c r="T63">
-        <v>1.516544557040179</v>
+        <v>1.556453624330709</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1154058325397892</v>
+        <v>0.1135444481439861</v>
       </c>
       <c r="W63">
-        <v>0.1776265088260103</v>
+        <v>0.1780002748126876</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5770291626989459</v>
+        <v>0.5677222407199306</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1659971721160769</v>
+        <v>0.1675471721160769</v>
       </c>
       <c r="C64">
-        <v>-419.1962531361231</v>
+        <v>-442.1149312270629</v>
       </c>
       <c r="D64">
-        <v>549.9577468638768</v>
+        <v>542.9560687729369</v>
       </c>
       <c r="E64">
-        <v>703.454</v>
+        <v>719.3709999999999</v>
       </c>
       <c r="F64">
-        <v>986.8539999999999</v>
+        <v>1002.771</v>
       </c>
       <c r="G64">
         <v>17.7</v>
@@ -6529,37 +6529,37 @@
         <v>112.5</v>
       </c>
       <c r="M64">
-        <v>198.1602832</v>
+        <v>201.3564168</v>
       </c>
       <c r="N64">
-        <v>-85.66028319999997</v>
+        <v>-88.85641679999996</v>
       </c>
       <c r="O64">
-        <v>-17.13205663999999</v>
+        <v>-17.77128335999999</v>
       </c>
       <c r="P64">
-        <v>-68.52822655999998</v>
+        <v>-71.08513343999996</v>
       </c>
       <c r="Q64">
-        <v>-23.82822655999998</v>
+        <v>-26.38513343999996</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1464131624531858</v>
+        <v>0.1491324371140827</v>
       </c>
       <c r="T64">
-        <v>1.556453624330709</v>
+        <v>1.59851993850181</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1135444481439861</v>
+        <v>0.1117421553163038</v>
       </c>
       <c r="W64">
-        <v>0.1780002748126876</v>
+        <v>0.1783621752124862</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5677222407199306</v>
+        <v>0.558710776581519</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1675471721160769</v>
+        <v>0.1690971721160769</v>
       </c>
       <c r="C65">
-        <v>-442.1149312270629</v>
+        <v>-464.8575695783283</v>
       </c>
       <c r="D65">
-        <v>542.9560687729369</v>
+        <v>536.1304304216716</v>
       </c>
       <c r="E65">
-        <v>719.3709999999999</v>
+        <v>735.2879999999999</v>
       </c>
       <c r="F65">
-        <v>1002.771</v>
+        <v>1018.688</v>
       </c>
       <c r="G65">
         <v>17.7</v>
@@ -6611,37 +6611,37 @@
         <v>112.5</v>
       </c>
       <c r="M65">
-        <v>201.3564168</v>
+        <v>204.5525504</v>
       </c>
       <c r="N65">
-        <v>-88.85641679999996</v>
+        <v>-92.05255039999996</v>
       </c>
       <c r="O65">
-        <v>-17.77128335999999</v>
+        <v>-18.41051007999999</v>
       </c>
       <c r="P65">
-        <v>-71.08513343999996</v>
+        <v>-73.64204031999996</v>
       </c>
       <c r="Q65">
-        <v>-26.38513343999996</v>
+        <v>-28.94204031999996</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1491324371140827</v>
+        <v>0.1520027825894739</v>
       </c>
       <c r="T65">
-        <v>1.59851993850181</v>
+        <v>1.64292327012686</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1117421553163038</v>
+        <v>0.1099961841394866</v>
       </c>
       <c r="W65">
-        <v>0.1783621752124862</v>
+        <v>0.1787127662247911</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.558710776581519</v>
+        <v>0.5499809206974329</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1690971721160769</v>
+        <v>0.1706471721160769</v>
       </c>
       <c r="C66">
-        <v>-464.8575695783283</v>
+        <v>-487.4307248846014</v>
       </c>
       <c r="D66">
-        <v>536.1304304216716</v>
+        <v>529.4742751153985</v>
       </c>
       <c r="E66">
-        <v>735.2879999999999</v>
+        <v>751.205</v>
       </c>
       <c r="F66">
-        <v>1018.688</v>
+        <v>1034.605</v>
       </c>
       <c r="G66">
         <v>17.7</v>
@@ -6693,37 +6693,37 @@
         <v>112.5</v>
       </c>
       <c r="M66">
-        <v>204.5525504</v>
+        <v>207.748684</v>
       </c>
       <c r="N66">
-        <v>-92.05255039999996</v>
+        <v>-95.24868399999998</v>
       </c>
       <c r="O66">
-        <v>-18.41051007999999</v>
+        <v>-19.0497368</v>
       </c>
       <c r="P66">
-        <v>-73.64204031999996</v>
+        <v>-76.19894719999999</v>
       </c>
       <c r="Q66">
-        <v>-28.94204031999996</v>
+        <v>-31.49894719999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1520027825894739</v>
+        <v>0.155037147806316</v>
       </c>
       <c r="T66">
-        <v>1.64292327012686</v>
+        <v>1.689863934987628</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1099961841394866</v>
+        <v>0.1083039351527252</v>
       </c>
       <c r="W66">
-        <v>0.1787127662247911</v>
+        <v>0.1790525698213328</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5499809206974329</v>
+        <v>0.541519675763626</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1706471721160769</v>
+        <v>0.1721971721160769</v>
       </c>
       <c r="C67">
-        <v>-487.4307248846014</v>
+        <v>-509.8406322233444</v>
       </c>
       <c r="D67">
-        <v>529.4742751153985</v>
+        <v>522.9813677766555</v>
       </c>
       <c r="E67">
-        <v>751.205</v>
+        <v>767.122</v>
       </c>
       <c r="F67">
-        <v>1034.605</v>
+        <v>1050.522</v>
       </c>
       <c r="G67">
         <v>17.7</v>
@@ -6775,37 +6775,37 @@
         <v>112.5</v>
       </c>
       <c r="M67">
-        <v>207.748684</v>
+        <v>210.9448176</v>
       </c>
       <c r="N67">
-        <v>-95.24868399999998</v>
+        <v>-98.44481759999998</v>
       </c>
       <c r="O67">
-        <v>-19.0497368</v>
+        <v>-19.68896352</v>
       </c>
       <c r="P67">
-        <v>-76.19894719999999</v>
+        <v>-78.75585407999998</v>
       </c>
       <c r="Q67">
-        <v>-31.49894719999999</v>
+        <v>-34.05585407999997</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.155037147806316</v>
+        <v>0.1582500050947371</v>
       </c>
       <c r="T67">
-        <v>1.689863934987628</v>
+        <v>1.73956581542844</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1083039351527252</v>
+        <v>0.10666296643829</v>
       </c>
       <c r="W67">
-        <v>0.1790525698213328</v>
+        <v>0.1793820763391914</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.541519675763626</v>
+        <v>0.5333148321914499</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1721971721160769</v>
+        <v>0.1737471721160769</v>
       </c>
       <c r="C68">
-        <v>-509.8406322233444</v>
+        <v>-532.0932245357591</v>
       </c>
       <c r="D68">
-        <v>522.9813677766555</v>
+        <v>516.6457754642407</v>
       </c>
       <c r="E68">
-        <v>767.122</v>
+        <v>783.0389999999999</v>
       </c>
       <c r="F68">
-        <v>1050.522</v>
+        <v>1066.439</v>
       </c>
       <c r="G68">
         <v>17.7</v>
@@ -6857,37 +6857,37 @@
         <v>112.5</v>
       </c>
       <c r="M68">
-        <v>210.9448176</v>
+        <v>214.1409512</v>
       </c>
       <c r="N68">
-        <v>-98.44481759999998</v>
+        <v>-101.6409512</v>
       </c>
       <c r="O68">
-        <v>-19.68896352</v>
+        <v>-20.32819024</v>
       </c>
       <c r="P68">
-        <v>-78.75585407999998</v>
+        <v>-81.31276095999998</v>
       </c>
       <c r="Q68">
-        <v>-34.05585407999997</v>
+        <v>-36.61276095999997</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1582500050947371</v>
+        <v>0.1616575810066988</v>
       </c>
       <c r="T68">
-        <v>1.73956581542844</v>
+        <v>1.792279931047484</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.10666296643829</v>
+        <v>0.1050709818645842</v>
       </c>
       <c r="W68">
-        <v>0.1793820763391914</v>
+        <v>0.1797017468415915</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5333148321914499</v>
+        <v>0.5253549093229208</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1737471721160769</v>
+        <v>0.1752971721160769</v>
       </c>
       <c r="C69">
-        <v>-532.0932245357591</v>
+        <v>-554.1941507086935</v>
       </c>
       <c r="D69">
-        <v>516.6457754642407</v>
+        <v>510.4618492913065</v>
       </c>
       <c r="E69">
-        <v>783.0389999999999</v>
+        <v>798.956</v>
       </c>
       <c r="F69">
-        <v>1066.439</v>
+        <v>1082.356</v>
       </c>
       <c r="G69">
         <v>17.7</v>
@@ -6939,37 +6939,37 @@
         <v>112.5</v>
       </c>
       <c r="M69">
-        <v>214.1409512</v>
+        <v>217.3370848</v>
       </c>
       <c r="N69">
-        <v>-101.6409512</v>
+        <v>-104.8370848</v>
       </c>
       <c r="O69">
-        <v>-20.32819024</v>
+        <v>-20.96741696</v>
       </c>
       <c r="P69">
-        <v>-81.31276095999998</v>
+        <v>-83.86966784000001</v>
       </c>
       <c r="Q69">
-        <v>-36.61276095999997</v>
+        <v>-39.16966784</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1616575810066988</v>
+        <v>0.1652781304131581</v>
       </c>
       <c r="T69">
-        <v>1.792279931047484</v>
+        <v>1.848288678892718</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1050709818645842</v>
+        <v>0.1035258203665756</v>
       </c>
       <c r="W69">
-        <v>0.1797017468415915</v>
+        <v>0.1800120152703917</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5253549093229208</v>
+        <v>0.5176291018328778</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1752971721160769</v>
+        <v>0.1768471721160769</v>
       </c>
       <c r="C70">
-        <v>-554.1941507086935</v>
+        <v>-576.1487923733351</v>
       </c>
       <c r="D70">
-        <v>510.4618492913065</v>
+        <v>504.4242076266647</v>
       </c>
       <c r="E70">
-        <v>798.956</v>
+        <v>814.8729999999999</v>
       </c>
       <c r="F70">
-        <v>1082.356</v>
+        <v>1098.273</v>
       </c>
       <c r="G70">
         <v>17.7</v>
@@ -7021,37 +7021,37 @@
         <v>112.5</v>
       </c>
       <c r="M70">
-        <v>217.3370848</v>
+        <v>220.5332184</v>
       </c>
       <c r="N70">
-        <v>-104.8370848</v>
+        <v>-108.0332184</v>
       </c>
       <c r="O70">
-        <v>-20.96741696</v>
+        <v>-21.60664367999999</v>
       </c>
       <c r="P70">
-        <v>-83.86966784000001</v>
+        <v>-86.42657471999998</v>
       </c>
       <c r="Q70">
-        <v>-39.16966784</v>
+        <v>-41.72657471999997</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1652781304131581</v>
+        <v>0.1691322636522923</v>
       </c>
       <c r="T70">
-        <v>1.848288678892718</v>
+        <v>1.90791089434087</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1035258203665756</v>
+        <v>0.1020254461583644</v>
       </c>
       <c r="W70">
-        <v>0.1800120152703917</v>
+        <v>0.1803132904114004</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5176291018328778</v>
+        <v>0.5101272307918217</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1768471721160769</v>
+        <v>0.1783971721160769</v>
       </c>
       <c r="C71">
-        <v>-576.1487923733351</v>
+        <v>-597.9622795256926</v>
       </c>
       <c r="D71">
-        <v>504.4242076266647</v>
+        <v>498.5277204743074</v>
       </c>
       <c r="E71">
-        <v>814.8729999999999</v>
+        <v>830.7900000000001</v>
       </c>
       <c r="F71">
-        <v>1098.273</v>
+        <v>1114.19</v>
       </c>
       <c r="G71">
         <v>17.7</v>
@@ -7103,37 +7103,37 @@
         <v>112.5</v>
       </c>
       <c r="M71">
-        <v>220.5332184</v>
+        <v>223.729352</v>
       </c>
       <c r="N71">
-        <v>-108.0332184</v>
+        <v>-111.229352</v>
       </c>
       <c r="O71">
-        <v>-21.60664367999999</v>
+        <v>-22.2458704</v>
       </c>
       <c r="P71">
-        <v>-86.42657471999998</v>
+        <v>-88.98348159999999</v>
       </c>
       <c r="Q71">
-        <v>-41.72657471999997</v>
+        <v>-44.28348159999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1691322636522923</v>
+        <v>0.1732433391073687</v>
       </c>
       <c r="T71">
-        <v>1.90791089434087</v>
+        <v>1.971507924152232</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1020254461583644</v>
+        <v>0.1005679397846734</v>
       </c>
       <c r="W71">
-        <v>0.1803132904114004</v>
+        <v>0.1806059576912376</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5101272307918217</v>
+        <v>0.502839698923367</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1783971721160769</v>
+        <v>0.2052269291340265</v>
       </c>
       <c r="C72">
-        <v>-597.9622795256926</v>
+        <v>-697.7758814341041</v>
       </c>
       <c r="D72">
-        <v>498.5277204743074</v>
+        <v>414.6311185658959</v>
       </c>
       <c r="E72">
-        <v>830.7900000000001</v>
+        <v>846.707</v>
       </c>
       <c r="F72">
-        <v>1114.19</v>
+        <v>1130.107</v>
       </c>
       <c r="G72">
         <v>17.7</v>
@@ -7185,45 +7185,45 @@
         <v>112.5</v>
       </c>
       <c r="M72">
-        <v>223.729352</v>
+        <v>266.4792306</v>
       </c>
       <c r="N72">
-        <v>-111.229352</v>
+        <v>-153.9792306</v>
       </c>
       <c r="O72">
-        <v>-22.2458704</v>
+        <v>-30.79584612</v>
       </c>
       <c r="P72">
-        <v>-88.98348159999999</v>
+        <v>-123.18338448</v>
       </c>
       <c r="Q72">
-        <v>-44.28348159999999</v>
+        <v>-78.48338448</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1732433391073687</v>
+        <v>0.1791198577591731</v>
       </c>
       <c r="T72">
-        <v>1.971507924152232</v>
+        <v>2.062415798738758</v>
       </c>
       <c r="U72">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.1005679397846734</v>
+        <v>0.08443434765756189</v>
       </c>
       <c r="W72">
-        <v>0.1806059576912376</v>
+        <v>0.2158903808223469</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y72">
-        <v>0.502839698923367</v>
+        <v>0.4221717382878094</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2052269291340265</v>
+        <v>0.2071269291340265</v>
       </c>
       <c r="C73">
-        <v>-697.7758814341037</v>
+        <v>-718.5761277061549</v>
       </c>
       <c r="D73">
-        <v>414.631118565896</v>
+        <v>409.7478722938449</v>
       </c>
       <c r="E73">
-        <v>846.7069999999998</v>
+        <v>862.6239999999999</v>
       </c>
       <c r="F73">
-        <v>1130.107</v>
+        <v>1146.024</v>
       </c>
       <c r="G73">
         <v>17.7</v>
@@ -7267,37 +7267,37 @@
         <v>112.5</v>
       </c>
       <c r="M73">
-        <v>266.4792305999999</v>
+        <v>270.2324592</v>
       </c>
       <c r="N73">
-        <v>-153.9792305999999</v>
+        <v>-157.7324592</v>
       </c>
       <c r="O73">
-        <v>-30.79584611999999</v>
+        <v>-31.54649184</v>
       </c>
       <c r="P73">
-        <v>-123.1833844799999</v>
+        <v>-126.18596736</v>
       </c>
       <c r="Q73">
-        <v>-78.48338447999994</v>
+        <v>-81.48596735999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.179119857759173</v>
+        <v>0.1838812812505721</v>
       </c>
       <c r="T73">
-        <v>2.062415798738757</v>
+        <v>2.13607350583657</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.08443434765756191</v>
+        <v>0.0832616483845402</v>
       </c>
       <c r="W73">
-        <v>0.2158903808223469</v>
+        <v>0.2161669033109254</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4221717382878094</v>
+        <v>0.4163082419227009</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2071269291340265</v>
+        <v>0.2090269291340265</v>
       </c>
       <c r="C74">
-        <v>-718.5761277061549</v>
+        <v>-739.262689698705</v>
       </c>
       <c r="D74">
-        <v>409.7478722938449</v>
+        <v>404.9783103012948</v>
       </c>
       <c r="E74">
-        <v>862.6239999999999</v>
+        <v>878.5409999999998</v>
       </c>
       <c r="F74">
-        <v>1146.024</v>
+        <v>1161.941</v>
       </c>
       <c r="G74">
         <v>17.7</v>
@@ -7349,37 +7349,37 @@
         <v>112.5</v>
       </c>
       <c r="M74">
-        <v>270.2324592</v>
+        <v>273.9856877999999</v>
       </c>
       <c r="N74">
-        <v>-157.7324592</v>
+        <v>-161.4856877999999</v>
       </c>
       <c r="O74">
-        <v>-31.54649184</v>
+        <v>-32.29713755999999</v>
       </c>
       <c r="P74">
-        <v>-126.18596736</v>
+        <v>-129.18855024</v>
       </c>
       <c r="Q74">
-        <v>-81.48596735999999</v>
+        <v>-84.48855023999995</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1838812812505721</v>
+        <v>0.188995402778371</v>
       </c>
       <c r="T74">
-        <v>2.13607350583657</v>
+        <v>2.215187339386072</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.0832616483845402</v>
+        <v>0.08212107785872459</v>
       </c>
       <c r="W74">
-        <v>0.2161669033109254</v>
+        <v>0.2164358498409127</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4163082419227009</v>
+        <v>0.4106053892936229</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2090269291340265</v>
+        <v>0.2109269291340265</v>
       </c>
       <c r="C75">
-        <v>-739.262689698705</v>
+        <v>-759.8394916680611</v>
       </c>
       <c r="D75">
-        <v>404.9783103012948</v>
+        <v>400.3185083319388</v>
       </c>
       <c r="E75">
-        <v>878.5409999999998</v>
+        <v>894.458</v>
       </c>
       <c r="F75">
-        <v>1161.941</v>
+        <v>1177.858</v>
       </c>
       <c r="G75">
         <v>17.7</v>
@@ -7431,37 +7431,37 @@
         <v>112.5</v>
       </c>
       <c r="M75">
-        <v>273.9856877999999</v>
+        <v>277.7389164</v>
       </c>
       <c r="N75">
-        <v>-161.4856877999999</v>
+        <v>-165.2389164</v>
       </c>
       <c r="O75">
-        <v>-32.29713755999999</v>
+        <v>-33.04778328</v>
       </c>
       <c r="P75">
-        <v>-129.18855024</v>
+        <v>-132.19113312</v>
       </c>
       <c r="Q75">
-        <v>-84.48855023999995</v>
+        <v>-87.49113311999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.188995402778371</v>
+        <v>0.1945029182698468</v>
       </c>
       <c r="T75">
-        <v>2.215187339386072</v>
+        <v>2.300386852439383</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.08212107785872459</v>
+        <v>0.08101133356333641</v>
       </c>
       <c r="W75">
-        <v>0.2164358498409127</v>
+        <v>0.2166975275457653</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4106053892936229</v>
+        <v>0.4050566678166819</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2109269291340265</v>
+        <v>0.2128269291340265</v>
       </c>
       <c r="C76">
-        <v>-759.8394916680611</v>
+        <v>-780.3102793104142</v>
       </c>
       <c r="D76">
-        <v>400.3185083319388</v>
+        <v>395.7647206895857</v>
       </c>
       <c r="E76">
-        <v>894.458</v>
+        <v>910.3749999999999</v>
       </c>
       <c r="F76">
-        <v>1177.858</v>
+        <v>1193.775</v>
       </c>
       <c r="G76">
         <v>17.7</v>
@@ -7513,37 +7513,37 @@
         <v>112.5</v>
       </c>
       <c r="M76">
-        <v>277.7389164</v>
+        <v>281.492145</v>
       </c>
       <c r="N76">
-        <v>-165.2389164</v>
+        <v>-168.992145</v>
       </c>
       <c r="O76">
-        <v>-33.04778328</v>
+        <v>-33.798429</v>
       </c>
       <c r="P76">
-        <v>-132.19113312</v>
+        <v>-135.193716</v>
       </c>
       <c r="Q76">
-        <v>-87.49113311999999</v>
+        <v>-90.49371599999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1945029182698468</v>
+        <v>0.2004510350006407</v>
       </c>
       <c r="T76">
-        <v>2.300386852439383</v>
+        <v>2.392402326536959</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.08101133356333641</v>
+        <v>0.07993118244915859</v>
       </c>
       <c r="W76">
-        <v>0.2166975275457653</v>
+        <v>0.2169522271784884</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4050566678166819</v>
+        <v>0.3996559122457929</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2128269291340265</v>
+        <v>0.2147269291340265</v>
       </c>
       <c r="C77">
-        <v>-780.3102793104142</v>
+        <v>-800.6786298035826</v>
       </c>
       <c r="D77">
-        <v>395.7647206895857</v>
+        <v>391.3133701964172</v>
       </c>
       <c r="E77">
-        <v>910.3749999999999</v>
+        <v>926.2919999999998</v>
       </c>
       <c r="F77">
-        <v>1193.775</v>
+        <v>1209.692</v>
       </c>
       <c r="G77">
         <v>17.7</v>
@@ -7595,37 +7595,37 @@
         <v>112.5</v>
       </c>
       <c r="M77">
-        <v>281.492145</v>
+        <v>285.2453735999999</v>
       </c>
       <c r="N77">
-        <v>-168.992145</v>
+        <v>-172.7453735999999</v>
       </c>
       <c r="O77">
-        <v>-33.798429</v>
+        <v>-34.54907471999999</v>
       </c>
       <c r="P77">
-        <v>-135.193716</v>
+        <v>-138.1962988799999</v>
       </c>
       <c r="Q77">
-        <v>-90.49371599999999</v>
+        <v>-93.49629887999994</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2004510350006407</v>
+        <v>0.2068948281256674</v>
       </c>
       <c r="T77">
-        <v>2.392402326536959</v>
+        <v>2.492085756809332</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.07993118244915859</v>
+        <v>0.07887945636430126</v>
       </c>
       <c r="W77">
-        <v>0.2169522271784884</v>
+        <v>0.2172002241892978</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3996559122457929</v>
+        <v>0.3943972818215062</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2147269291340265</v>
+        <v>0.2166269291340265</v>
       </c>
       <c r="C78">
-        <v>-800.6786298035826</v>
+        <v>-820.9479611786312</v>
       </c>
       <c r="D78">
-        <v>391.3133701964172</v>
+        <v>386.9610388213687</v>
       </c>
       <c r="E78">
-        <v>926.2919999999998</v>
+        <v>942.2089999999999</v>
       </c>
       <c r="F78">
-        <v>1209.692</v>
+        <v>1225.609</v>
       </c>
       <c r="G78">
         <v>17.7</v>
@@ -7677,37 +7677,37 @@
         <v>112.5</v>
       </c>
       <c r="M78">
-        <v>285.2453735999999</v>
+        <v>288.9986022</v>
       </c>
       <c r="N78">
-        <v>-172.7453735999999</v>
+        <v>-176.4986022</v>
       </c>
       <c r="O78">
-        <v>-34.54907471999999</v>
+        <v>-35.29972044</v>
       </c>
       <c r="P78">
-        <v>-138.1962988799999</v>
+        <v>-141.19888176</v>
       </c>
       <c r="Q78">
-        <v>-93.49629887999994</v>
+        <v>-96.49888176</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2068948281256674</v>
+        <v>0.213898951087653</v>
       </c>
       <c r="T78">
-        <v>2.492085756809332</v>
+        <v>2.600437311453216</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.07887945636430126</v>
+        <v>0.07785504784008954</v>
       </c>
       <c r="W78">
-        <v>0.2172002241892978</v>
+        <v>0.2174417797193069</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3943972818215062</v>
+        <v>0.3892752392004476</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2166269291340265</v>
+        <v>0.2185269291340265</v>
       </c>
       <c r="C79">
-        <v>-820.9479611786312</v>
+        <v>-841.1215410729574</v>
       </c>
       <c r="D79">
-        <v>386.9610388213687</v>
+        <v>382.7044589270424</v>
       </c>
       <c r="E79">
-        <v>942.2089999999999</v>
+        <v>958.1259999999999</v>
       </c>
       <c r="F79">
-        <v>1225.609</v>
+        <v>1241.526</v>
       </c>
       <c r="G79">
         <v>17.7</v>
@@ -7759,37 +7759,37 @@
         <v>112.5</v>
       </c>
       <c r="M79">
-        <v>288.9986022</v>
+        <v>292.7518308</v>
       </c>
       <c r="N79">
-        <v>-176.4986022</v>
+        <v>-180.2518308</v>
       </c>
       <c r="O79">
-        <v>-35.29972044</v>
+        <v>-36.05036616</v>
       </c>
       <c r="P79">
-        <v>-141.19888176</v>
+        <v>-144.20146464</v>
       </c>
       <c r="Q79">
-        <v>-96.49888176</v>
+        <v>-99.50146463999998</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.213898951087653</v>
+        <v>0.2215398125007281</v>
       </c>
       <c r="T79">
-        <v>2.600437311453216</v>
+        <v>2.718639007428362</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.07785504784008954</v>
+        <v>0.07685690620111403</v>
       </c>
       <c r="W79">
-        <v>0.2174417797193069</v>
+        <v>0.2176771415177773</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3892752392004476</v>
+        <v>0.38428453100557</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2185269291340265</v>
+        <v>0.2204269291340265</v>
       </c>
       <c r="C80">
-        <v>-841.1215410729574</v>
+        <v>-861.2024949119631</v>
       </c>
       <c r="D80">
-        <v>382.7044589270424</v>
+        <v>378.5405050880369</v>
       </c>
       <c r="E80">
-        <v>958.1259999999999</v>
+        <v>974.043</v>
       </c>
       <c r="F80">
-        <v>1241.526</v>
+        <v>1257.443</v>
       </c>
       <c r="G80">
         <v>17.7</v>
@@ -7841,37 +7841,37 @@
         <v>112.5</v>
       </c>
       <c r="M80">
-        <v>292.7518308</v>
+        <v>296.5050594</v>
       </c>
       <c r="N80">
-        <v>-180.2518308</v>
+        <v>-184.0050594</v>
       </c>
       <c r="O80">
-        <v>-36.05036616</v>
+        <v>-36.80101188</v>
       </c>
       <c r="P80">
-        <v>-144.20146464</v>
+        <v>-147.20404752</v>
       </c>
       <c r="Q80">
-        <v>-99.50146463999998</v>
+        <v>-102.50404752</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2215398125007281</v>
+        <v>0.2299083750007628</v>
       </c>
       <c r="T80">
-        <v>2.718639007428362</v>
+        <v>2.848098007782094</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07685690620111403</v>
+        <v>0.07588403397072019</v>
       </c>
       <c r="W80">
-        <v>0.2176771415177773</v>
+        <v>0.2179065447897042</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.38428453100557</v>
+        <v>0.3794201698536008</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2204269291340265</v>
+        <v>0.2223269291340265</v>
       </c>
       <c r="C81">
-        <v>-861.2024949119631</v>
+        <v>-881.1938135623556</v>
       </c>
       <c r="D81">
-        <v>378.5405050880369</v>
+        <v>374.4661864376444</v>
       </c>
       <c r="E81">
-        <v>974.043</v>
+        <v>989.9599999999999</v>
       </c>
       <c r="F81">
-        <v>1257.443</v>
+        <v>1273.36</v>
       </c>
       <c r="G81">
         <v>17.7</v>
@@ -7923,37 +7923,37 @@
         <v>112.5</v>
       </c>
       <c r="M81">
-        <v>296.5050594</v>
+        <v>300.258288</v>
       </c>
       <c r="N81">
-        <v>-184.0050594</v>
+        <v>-187.758288</v>
       </c>
       <c r="O81">
-        <v>-36.80101188</v>
+        <v>-37.5516576</v>
       </c>
       <c r="P81">
-        <v>-147.20404752</v>
+        <v>-150.2066304</v>
       </c>
       <c r="Q81">
-        <v>-102.50404752</v>
+        <v>-105.5066304</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2299083750007628</v>
+        <v>0.239113793750801</v>
       </c>
       <c r="T81">
-        <v>2.848098007782094</v>
+        <v>2.990502908171199</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.07588403397072019</v>
+        <v>0.07493548354608617</v>
       </c>
       <c r="W81">
-        <v>0.2179065447897042</v>
+        <v>0.2181302129798329</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3794201698536008</v>
+        <v>0.3746774177304308</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2223269291340265</v>
+        <v>0.2242269291340265</v>
       </c>
       <c r="C82">
-        <v>-881.1938135623556</v>
+        <v>-901.0983604964683</v>
       </c>
       <c r="D82">
-        <v>374.4661864376444</v>
+        <v>370.4786395035317</v>
       </c>
       <c r="E82">
-        <v>989.9599999999999</v>
+        <v>1005.877</v>
       </c>
       <c r="F82">
-        <v>1273.36</v>
+        <v>1289.277</v>
       </c>
       <c r="G82">
         <v>17.7</v>
@@ -8005,37 +8005,37 @@
         <v>112.5</v>
       </c>
       <c r="M82">
-        <v>300.258288</v>
+        <v>304.0115166</v>
       </c>
       <c r="N82">
-        <v>-187.758288</v>
+        <v>-191.5115166</v>
       </c>
       <c r="O82">
-        <v>-37.5516576</v>
+        <v>-38.30230332000001</v>
       </c>
       <c r="P82">
-        <v>-150.2066304</v>
+        <v>-153.20921328</v>
       </c>
       <c r="Q82">
-        <v>-105.5066304</v>
+        <v>-108.50921328</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.239113793750801</v>
+        <v>0.2492882039482116</v>
       </c>
       <c r="T82">
-        <v>2.990502908171199</v>
+        <v>3.147897798074947</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.07493548354608617</v>
+        <v>0.07401035411959127</v>
       </c>
       <c r="W82">
-        <v>0.2181302129798329</v>
+        <v>0.2183483584986004</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3746774177304308</v>
+        <v>0.3700517705979562</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2242269291340265</v>
+        <v>0.2261269291340265</v>
       </c>
       <c r="C83">
-        <v>-901.0983604964683</v>
+        <v>-920.9188785036622</v>
       </c>
       <c r="D83">
-        <v>370.4786395035317</v>
+        <v>366.5751214963378</v>
       </c>
       <c r="E83">
-        <v>1005.877</v>
+        <v>1021.794</v>
       </c>
       <c r="F83">
-        <v>1289.277</v>
+        <v>1305.194</v>
       </c>
       <c r="G83">
         <v>17.7</v>
@@ -8087,37 +8087,37 @@
         <v>112.5</v>
       </c>
       <c r="M83">
-        <v>304.0115166</v>
+        <v>307.7647452</v>
       </c>
       <c r="N83">
-        <v>-191.5115166</v>
+        <v>-195.2647452</v>
       </c>
       <c r="O83">
-        <v>-38.30230332000001</v>
+        <v>-39.05294904</v>
       </c>
       <c r="P83">
-        <v>-153.20921328</v>
+        <v>-156.21179616</v>
       </c>
       <c r="Q83">
-        <v>-108.50921328</v>
+        <v>-111.51179616</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2492882039482116</v>
+        <v>0.2605931041675567</v>
       </c>
       <c r="T83">
-        <v>3.147897798074947</v>
+        <v>3.322781009079111</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07401035411959127</v>
+        <v>0.07310778882544992</v>
       </c>
       <c r="W83">
-        <v>0.2183483584986004</v>
+        <v>0.2185611833949589</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3700517705979562</v>
+        <v>0.3655389441272496</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2261269291340265</v>
+        <v>0.2280269291340265</v>
       </c>
       <c r="C84">
-        <v>-920.9188785036622</v>
+        <v>-940.6579959818687</v>
       </c>
       <c r="D84">
-        <v>366.5751214963378</v>
+        <v>362.7530040181312</v>
       </c>
       <c r="E84">
-        <v>1021.794</v>
+        <v>1037.711</v>
       </c>
       <c r="F84">
-        <v>1305.194</v>
+        <v>1321.111</v>
       </c>
       <c r="G84">
         <v>17.7</v>
@@ -8169,37 +8169,37 @@
         <v>112.5</v>
       </c>
       <c r="M84">
-        <v>307.7647452</v>
+        <v>311.5179738</v>
       </c>
       <c r="N84">
-        <v>-195.2647452</v>
+        <v>-199.0179738</v>
       </c>
       <c r="O84">
-        <v>-39.05294904</v>
+        <v>-39.80359476</v>
       </c>
       <c r="P84">
-        <v>-156.21179616</v>
+        <v>-159.21437904</v>
       </c>
       <c r="Q84">
-        <v>-111.51179616</v>
+        <v>-114.51437904</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2605931041675567</v>
+        <v>0.2732279926480011</v>
       </c>
       <c r="T84">
-        <v>3.322781009079111</v>
+        <v>3.518238715495529</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07310778882544992</v>
+        <v>0.07222697209261318</v>
       </c>
       <c r="W84">
-        <v>0.2185611833949589</v>
+        <v>0.2187688799805618</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3655389441272496</v>
+        <v>0.3611348604630659</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2280269291340265</v>
+        <v>0.2299269291340265</v>
       </c>
       <c r="C85">
-        <v>-940.6579959818687</v>
+        <v>-960.3182328395952</v>
       </c>
       <c r="D85">
-        <v>362.7530040181312</v>
+        <v>359.0097671604048</v>
       </c>
       <c r="E85">
-        <v>1037.711</v>
+        <v>1053.628</v>
       </c>
       <c r="F85">
-        <v>1321.111</v>
+        <v>1337.028</v>
       </c>
       <c r="G85">
         <v>17.7</v>
@@ -8251,37 +8251,37 @@
         <v>112.5</v>
       </c>
       <c r="M85">
-        <v>311.5179738</v>
+        <v>315.2712024</v>
       </c>
       <c r="N85">
-        <v>-199.0179738</v>
+        <v>-202.7712024</v>
       </c>
       <c r="O85">
-        <v>-39.80359476</v>
+        <v>-40.55424048</v>
       </c>
       <c r="P85">
-        <v>-159.21437904</v>
+        <v>-162.21696192</v>
       </c>
       <c r="Q85">
-        <v>-114.51437904</v>
+        <v>-117.51696192</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2732279926480011</v>
+        <v>0.2874422421885013</v>
       </c>
       <c r="T85">
-        <v>3.518238715495529</v>
+        <v>3.738128635214</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07222697209261318</v>
+        <v>0.07136712718674874</v>
       </c>
       <c r="W85">
-        <v>0.2187688799805618</v>
+        <v>0.2189716314093647</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3611348604630659</v>
+        <v>0.3568356359337437</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2299269291340265</v>
+        <v>0.2318269291340265</v>
       </c>
       <c r="C86">
-        <v>-960.318232839595</v>
+        <v>-979.9020060362502</v>
       </c>
       <c r="D86">
-        <v>359.0097671604048</v>
+        <v>355.3429939637494</v>
       </c>
       <c r="E86">
-        <v>1053.628</v>
+        <v>1069.545</v>
       </c>
       <c r="F86">
-        <v>1337.028</v>
+        <v>1352.945</v>
       </c>
       <c r="G86">
         <v>17.7</v>
@@ -8333,37 +8333,37 @@
         <v>112.5</v>
       </c>
       <c r="M86">
-        <v>315.2712023999999</v>
+        <v>319.0244309999999</v>
       </c>
       <c r="N86">
-        <v>-202.7712023999999</v>
+        <v>-206.5244309999999</v>
       </c>
       <c r="O86">
-        <v>-40.55424047999999</v>
+        <v>-41.30488619999999</v>
       </c>
       <c r="P86">
-        <v>-162.21696192</v>
+        <v>-165.2195447999999</v>
       </c>
       <c r="Q86">
-        <v>-117.51696192</v>
+        <v>-120.5195447999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2874422421885011</v>
+        <v>0.3035517250010679</v>
       </c>
       <c r="T86">
-        <v>3.738128635213998</v>
+        <v>3.987337210894931</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07136712718674874</v>
+        <v>0.07052751392572819</v>
       </c>
       <c r="W86">
-        <v>0.2189716314093647</v>
+        <v>0.2191696122163133</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3568356359337437</v>
+        <v>0.3526375696286408</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2318269291340265</v>
+        <v>0.2337269291340265</v>
       </c>
       <c r="C87">
-        <v>-979.9020060362502</v>
+        <v>-999.4116347863836</v>
       </c>
       <c r="D87">
-        <v>355.3429939637494</v>
+        <v>351.7503652136162</v>
       </c>
       <c r="E87">
-        <v>1069.545</v>
+        <v>1085.462</v>
       </c>
       <c r="F87">
-        <v>1352.945</v>
+        <v>1368.862</v>
       </c>
       <c r="G87">
         <v>17.7</v>
@@ -8415,37 +8415,37 @@
         <v>112.5</v>
       </c>
       <c r="M87">
-        <v>319.0244309999999</v>
+        <v>322.7776596</v>
       </c>
       <c r="N87">
-        <v>-206.5244309999999</v>
+        <v>-210.2776596</v>
       </c>
       <c r="O87">
-        <v>-41.30488619999999</v>
+        <v>-42.05553192</v>
       </c>
       <c r="P87">
-        <v>-165.2195447999999</v>
+        <v>-168.22212768</v>
       </c>
       <c r="Q87">
-        <v>-120.5195447999999</v>
+        <v>-123.52212768</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3035517250010679</v>
+        <v>0.3219625625011441</v>
       </c>
       <c r="T87">
-        <v>3.987337210894931</v>
+        <v>4.27214701167314</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07052751392572819</v>
+        <v>0.06970742655449877</v>
       </c>
       <c r="W87">
-        <v>0.2191696122163133</v>
+        <v>0.2193629888184492</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3526375696286408</v>
+        <v>0.3485371327724938</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2337269291340265</v>
+        <v>0.2356269291340265</v>
       </c>
       <c r="C88">
-        <v>-999.4116347863836</v>
+        <v>-1018.849345451381</v>
       </c>
       <c r="D88">
-        <v>351.7503652136162</v>
+        <v>348.229654548619</v>
       </c>
       <c r="E88">
-        <v>1085.462</v>
+        <v>1101.379</v>
       </c>
       <c r="F88">
-        <v>1368.862</v>
+        <v>1384.779</v>
       </c>
       <c r="G88">
         <v>17.7</v>
@@ -8497,37 +8497,37 @@
         <v>112.5</v>
       </c>
       <c r="M88">
-        <v>322.7776596</v>
+        <v>326.5308881999999</v>
       </c>
       <c r="N88">
-        <v>-210.2776596</v>
+        <v>-214.0308881999999</v>
       </c>
       <c r="O88">
-        <v>-42.05553192</v>
+        <v>-42.80617763999999</v>
       </c>
       <c r="P88">
-        <v>-168.22212768</v>
+        <v>-171.2247105599999</v>
       </c>
       <c r="Q88">
-        <v>-123.52212768</v>
+        <v>-126.5247105599999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3219625625011441</v>
+        <v>0.3432058365396937</v>
       </c>
       <c r="T88">
-        <v>4.27214701167314</v>
+        <v>4.600773704878766</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.06970742655449877</v>
+        <v>0.06890619176651604</v>
       </c>
       <c r="W88">
-        <v>0.2193629888184492</v>
+        <v>0.2195519199814555</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3485371327724938</v>
+        <v>0.3445309588325801</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2356269291340265</v>
+        <v>0.2375269291340265</v>
       </c>
       <c r="C89">
-        <v>-1018.849345451381</v>
+        <v>-1038.217276140308</v>
       </c>
       <c r="D89">
-        <v>348.229654548619</v>
+        <v>344.7787238596921</v>
       </c>
       <c r="E89">
-        <v>1101.379</v>
+        <v>1117.296</v>
       </c>
       <c r="F89">
-        <v>1384.779</v>
+        <v>1400.696</v>
       </c>
       <c r="G89">
         <v>17.7</v>
@@ -8579,37 +8579,37 @@
         <v>112.5</v>
       </c>
       <c r="M89">
-        <v>326.5308881999999</v>
+        <v>330.2841168</v>
       </c>
       <c r="N89">
-        <v>-214.0308881999999</v>
+        <v>-217.7841168</v>
       </c>
       <c r="O89">
-        <v>-42.80617763999999</v>
+        <v>-43.55682336</v>
       </c>
       <c r="P89">
-        <v>-171.2247105599999</v>
+        <v>-174.22729344</v>
       </c>
       <c r="Q89">
-        <v>-126.5247105599999</v>
+        <v>-129.52729344</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3432058365396937</v>
+        <v>0.3679896562513348</v>
       </c>
       <c r="T89">
-        <v>4.600773704878766</v>
+        <v>4.984171513618664</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06890619176651604</v>
+        <v>0.06812316686007834</v>
       </c>
       <c r="W89">
-        <v>0.2195519199814555</v>
+        <v>0.2197365572543935</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3445309588325801</v>
+        <v>0.3406158343003917</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2375269291340265</v>
+        <v>0.2394269291340265</v>
       </c>
       <c r="C90">
-        <v>-1038.217276140308</v>
+        <v>-1057.51748103987</v>
       </c>
       <c r="D90">
-        <v>344.7787238596921</v>
+        <v>341.3955189601299</v>
       </c>
       <c r="E90">
-        <v>1117.296</v>
+        <v>1133.213</v>
       </c>
       <c r="F90">
-        <v>1400.696</v>
+        <v>1416.613</v>
       </c>
       <c r="G90">
         <v>17.7</v>
@@ -8661,37 +8661,37 @@
         <v>112.5</v>
       </c>
       <c r="M90">
-        <v>330.2841168</v>
+        <v>334.0373454</v>
       </c>
       <c r="N90">
-        <v>-217.7841168</v>
+        <v>-221.5373454</v>
       </c>
       <c r="O90">
-        <v>-43.55682336</v>
+        <v>-44.30746908</v>
       </c>
       <c r="P90">
-        <v>-174.22729344</v>
+        <v>-177.22987632</v>
       </c>
       <c r="Q90">
-        <v>-129.52729344</v>
+        <v>-132.52987632</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3679896562513348</v>
+        <v>0.3972796250014562</v>
       </c>
       <c r="T90">
-        <v>4.984171513618664</v>
+        <v>5.437278014856725</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.06812316686007834</v>
+        <v>0.06735773801895387</v>
       </c>
       <c r="W90">
-        <v>0.2197365572543935</v>
+        <v>0.2199170453751307</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3406158343003917</v>
+        <v>0.3367886900947693</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2394269291340265</v>
+        <v>0.2413269291340265</v>
       </c>
       <c r="C91">
-        <v>-1057.51748103987</v>
+        <v>-1076.75193449192</v>
       </c>
       <c r="D91">
-        <v>341.3955189601299</v>
+        <v>338.0780655080804</v>
       </c>
       <c r="E91">
-        <v>1133.213</v>
+        <v>1149.13</v>
       </c>
       <c r="F91">
-        <v>1416.613</v>
+        <v>1432.53</v>
       </c>
       <c r="G91">
         <v>17.7</v>
@@ -8743,37 +8743,37 @@
         <v>112.5</v>
       </c>
       <c r="M91">
-        <v>334.0373454</v>
+        <v>337.790574</v>
       </c>
       <c r="N91">
-        <v>-221.5373454</v>
+        <v>-225.290574</v>
       </c>
       <c r="O91">
-        <v>-44.30746908</v>
+        <v>-45.0581148</v>
       </c>
       <c r="P91">
-        <v>-177.22987632</v>
+        <v>-180.2324592</v>
       </c>
       <c r="Q91">
-        <v>-132.52987632</v>
+        <v>-135.5324592</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3972796250014562</v>
+        <v>0.4324275875016019</v>
       </c>
       <c r="T91">
-        <v>5.437278014856725</v>
+        <v>5.981005816342398</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06735773801895387</v>
+        <v>0.06660931870763216</v>
       </c>
       <c r="W91">
-        <v>0.2199170453751307</v>
+        <v>0.2200935226487403</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3367886900947693</v>
+        <v>0.3330465935381607</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2413269291340265</v>
+        <v>0.2432269291340265</v>
       </c>
       <c r="C92">
-        <v>-1076.75193449192</v>
+        <v>-1095.922534835514</v>
       </c>
       <c r="D92">
-        <v>338.0780655080804</v>
+        <v>334.8244651644855</v>
       </c>
       <c r="E92">
-        <v>1149.13</v>
+        <v>1165.047</v>
       </c>
       <c r="F92">
-        <v>1432.53</v>
+        <v>1448.447</v>
       </c>
       <c r="G92">
         <v>17.7</v>
@@ -8825,37 +8825,37 @@
         <v>112.5</v>
       </c>
       <c r="M92">
-        <v>337.790574</v>
+        <v>341.5438026</v>
       </c>
       <c r="N92">
-        <v>-225.290574</v>
+        <v>-229.0438026</v>
       </c>
       <c r="O92">
-        <v>-45.0581148</v>
+        <v>-45.80876052</v>
       </c>
       <c r="P92">
-        <v>-180.2324592</v>
+        <v>-183.23504208</v>
       </c>
       <c r="Q92">
-        <v>-135.5324592</v>
+        <v>-138.53504208</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4324275875016019</v>
+        <v>0.4753862083351132</v>
       </c>
       <c r="T92">
-        <v>5.981005816342398</v>
+        <v>6.64556201815822</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06660931870763216</v>
+        <v>0.06587734817238344</v>
       </c>
       <c r="W92">
-        <v>0.2200935226487403</v>
+        <v>0.220266121300952</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3330465935381607</v>
+        <v>0.3293867408619172</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2432269291340265</v>
+        <v>0.2451269291340265</v>
       </c>
       <c r="C93">
-        <v>-1095.922534835514</v>
+        <v>-1115.031108029243</v>
       </c>
       <c r="D93">
-        <v>334.8244651644855</v>
+        <v>331.6328919707566</v>
       </c>
       <c r="E93">
-        <v>1165.047</v>
+        <v>1180.964</v>
       </c>
       <c r="F93">
-        <v>1448.447</v>
+        <v>1464.364</v>
       </c>
       <c r="G93">
         <v>17.7</v>
@@ -8907,37 +8907,37 @@
         <v>112.5</v>
       </c>
       <c r="M93">
-        <v>341.5438026</v>
+        <v>345.2970312</v>
       </c>
       <c r="N93">
-        <v>-229.0438026</v>
+        <v>-232.7970312</v>
       </c>
       <c r="O93">
-        <v>-45.80876052</v>
+        <v>-46.55940624</v>
       </c>
       <c r="P93">
-        <v>-183.23504208</v>
+        <v>-186.23762496</v>
       </c>
       <c r="Q93">
-        <v>-138.53504208</v>
+        <v>-141.53762496</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4753862083351132</v>
+        <v>0.5290844843770025</v>
       </c>
       <c r="T93">
-        <v>6.64556201815822</v>
+        <v>7.476257270427999</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06587734817238344</v>
+        <v>0.06516129004007494</v>
       </c>
       <c r="W93">
-        <v>0.220266121300952</v>
+        <v>0.2204349678085503</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3293867408619172</v>
+        <v>0.3258064502003746</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2451269291340265</v>
+        <v>0.2470269291340265</v>
       </c>
       <c r="C94">
-        <v>-1115.031108029243</v>
+        <v>-1134.079411068335</v>
       </c>
       <c r="D94">
-        <v>331.6328919707566</v>
+        <v>328.5015889316647</v>
       </c>
       <c r="E94">
-        <v>1180.964</v>
+        <v>1196.881</v>
       </c>
       <c r="F94">
-        <v>1464.364</v>
+        <v>1480.281</v>
       </c>
       <c r="G94">
         <v>17.7</v>
@@ -8989,37 +8989,37 @@
         <v>112.5</v>
       </c>
       <c r="M94">
-        <v>345.2970312</v>
+        <v>349.0502598</v>
       </c>
       <c r="N94">
-        <v>-232.7970312</v>
+        <v>-236.5502598</v>
       </c>
       <c r="O94">
-        <v>-46.55940624</v>
+        <v>-47.31005196</v>
       </c>
       <c r="P94">
-        <v>-186.23762496</v>
+        <v>-189.24020784</v>
       </c>
       <c r="Q94">
-        <v>-141.53762496</v>
+        <v>-144.54020784</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5290844843770025</v>
+        <v>0.5981251250022886</v>
       </c>
       <c r="T94">
-        <v>7.476257270427999</v>
+        <v>8.544294023346287</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06516129004007494</v>
+        <v>0.06446063100738596</v>
       </c>
       <c r="W94">
-        <v>0.2204349678085503</v>
+        <v>0.2206001832084584</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3258064502003746</v>
+        <v>0.3223031550369297</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2470269291340265</v>
+        <v>0.2489269291340265</v>
       </c>
       <c r="C95">
-        <v>-1134.079411068335</v>
+        <v>-1153.069135209989</v>
       </c>
       <c r="D95">
-        <v>328.5015889316647</v>
+        <v>325.428864790011</v>
       </c>
       <c r="E95">
-        <v>1196.881</v>
+        <v>1212.798</v>
       </c>
       <c r="F95">
-        <v>1480.281</v>
+        <v>1496.198</v>
       </c>
       <c r="G95">
         <v>17.7</v>
@@ -9071,37 +9071,37 @@
         <v>112.5</v>
       </c>
       <c r="M95">
-        <v>349.0502598</v>
+        <v>352.8034884</v>
       </c>
       <c r="N95">
-        <v>-236.5502598</v>
+        <v>-240.3034884</v>
       </c>
       <c r="O95">
-        <v>-47.31005196</v>
+        <v>-48.06069768</v>
       </c>
       <c r="P95">
-        <v>-189.24020784</v>
+        <v>-192.24279072</v>
       </c>
       <c r="Q95">
-        <v>-144.54020784</v>
+        <v>-147.54279072</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5981251250022886</v>
+        <v>0.6901793125026702</v>
       </c>
       <c r="T95">
-        <v>8.544294023346287</v>
+        <v>9.968343027237337</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06446063100738596</v>
+        <v>0.06377487961369037</v>
       </c>
       <c r="W95">
-        <v>0.2206001832084584</v>
+        <v>0.2207618833870918</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3223031550369297</v>
+        <v>0.3188743980684517</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2489269291340265</v>
+        <v>0.2508269291340265</v>
       </c>
       <c r="C96">
-        <v>-1153.069135209989</v>
+        <v>-1172.001909019374</v>
       </c>
       <c r="D96">
-        <v>325.428864790011</v>
+        <v>322.4130909806259</v>
       </c>
       <c r="E96">
-        <v>1212.798</v>
+        <v>1228.715</v>
       </c>
       <c r="F96">
-        <v>1496.198</v>
+        <v>1512.115</v>
       </c>
       <c r="G96">
         <v>17.7</v>
@@ -9153,37 +9153,37 @@
         <v>112.5</v>
       </c>
       <c r="M96">
-        <v>352.8034884</v>
+        <v>356.556717</v>
       </c>
       <c r="N96">
-        <v>-240.3034884</v>
+        <v>-244.056717</v>
       </c>
       <c r="O96">
-        <v>-48.06069768</v>
+        <v>-48.8113434</v>
       </c>
       <c r="P96">
-        <v>-192.24279072</v>
+        <v>-195.2453736</v>
       </c>
       <c r="Q96">
-        <v>-147.54279072</v>
+        <v>-150.5453736</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6901793125026702</v>
+        <v>0.8190551750032047</v>
       </c>
       <c r="T96">
-        <v>9.968343027237337</v>
+        <v>11.96201163268481</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06377487961369037</v>
+        <v>0.06310356509144098</v>
       </c>
       <c r="W96">
-        <v>0.2207618833870918</v>
+        <v>0.2209201793514382</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3188743980684517</v>
+        <v>0.3155178254572049</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2508269291340265</v>
+        <v>0.2527269291340265</v>
       </c>
       <c r="C97">
-        <v>-1172.001909019374</v>
+        <v>-1190.879301247813</v>
       </c>
       <c r="D97">
-        <v>322.4130909806259</v>
+        <v>319.4526987521865</v>
       </c>
       <c r="E97">
-        <v>1228.715</v>
+        <v>1244.632</v>
       </c>
       <c r="F97">
-        <v>1512.115</v>
+        <v>1528.032</v>
       </c>
       <c r="G97">
         <v>17.7</v>
@@ -9235,37 +9235,37 @@
         <v>112.5</v>
       </c>
       <c r="M97">
-        <v>356.556717</v>
+        <v>360.3099456</v>
       </c>
       <c r="N97">
-        <v>-244.056717</v>
+        <v>-247.8099456</v>
       </c>
       <c r="O97">
-        <v>-48.8113434</v>
+        <v>-49.56198912</v>
       </c>
       <c r="P97">
-        <v>-195.2453736</v>
+        <v>-198.24795648</v>
       </c>
       <c r="Q97">
-        <v>-150.5453736</v>
+        <v>-153.54795648</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8190551750032047</v>
+        <v>1.012368968754006</v>
       </c>
       <c r="T97">
-        <v>11.96201163268481</v>
+        <v>14.95251454085602</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06310356509144098</v>
+        <v>0.06244623628840515</v>
       </c>
       <c r="W97">
-        <v>0.2209201793514382</v>
+        <v>0.2210751774831941</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3155178254572049</v>
+        <v>0.3122311814420257</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2527269291340265</v>
+        <v>0.2546269291340265</v>
       </c>
       <c r="C98">
-        <v>-1190.879301247813</v>
+        <v>-1209.70282355385</v>
       </c>
       <c r="D98">
-        <v>319.4526987521865</v>
+        <v>316.54617644615</v>
       </c>
       <c r="E98">
-        <v>1244.632</v>
+        <v>1260.549</v>
       </c>
       <c r="F98">
-        <v>1528.032</v>
+        <v>1543.949</v>
       </c>
       <c r="G98">
         <v>17.7</v>
@@ -9317,37 +9317,37 @@
         <v>112.5</v>
       </c>
       <c r="M98">
-        <v>360.3099455999999</v>
+        <v>364.0631742</v>
       </c>
       <c r="N98">
-        <v>-247.8099455999999</v>
+        <v>-251.5631742</v>
       </c>
       <c r="O98">
-        <v>-49.56198911999999</v>
+        <v>-50.31263484</v>
       </c>
       <c r="P98">
-        <v>-198.2479564799999</v>
+        <v>-201.25053936</v>
       </c>
       <c r="Q98">
-        <v>-153.5479564799999</v>
+        <v>-156.55053936</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.012368968754004</v>
+        <v>1.334558625005339</v>
       </c>
       <c r="T98">
-        <v>14.95251454085598</v>
+        <v>19.93668605447464</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06244623628840516</v>
+        <v>0.06180246065656592</v>
       </c>
       <c r="W98">
-        <v>0.2210751774831941</v>
+        <v>0.2212269797771818</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3122311814420258</v>
+        <v>0.3090123032828296</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2546269291340265</v>
+        <v>0.2565269291340265</v>
       </c>
       <c r="C99">
-        <v>-1209.70282355385</v>
+        <v>-1228.473933077105</v>
       </c>
       <c r="D99">
-        <v>316.54617644615</v>
+        <v>313.692066922895</v>
       </c>
       <c r="E99">
-        <v>1260.549</v>
+        <v>1276.466</v>
       </c>
       <c r="F99">
-        <v>1543.949</v>
+        <v>1559.866</v>
       </c>
       <c r="G99">
         <v>17.7</v>
@@ -9399,37 +9399,37 @@
         <v>112.5</v>
       </c>
       <c r="M99">
-        <v>364.0631742</v>
+        <v>367.8164027999999</v>
       </c>
       <c r="N99">
-        <v>-251.5631742</v>
+        <v>-255.3164027999999</v>
       </c>
       <c r="O99">
-        <v>-50.31263484</v>
+        <v>-51.06328055999999</v>
       </c>
       <c r="P99">
-        <v>-201.25053936</v>
+        <v>-204.25312224</v>
       </c>
       <c r="Q99">
-        <v>-156.55053936</v>
+        <v>-159.5531222399999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.334558625005339</v>
+        <v>1.978937937508007</v>
       </c>
       <c r="T99">
-        <v>19.93668605447464</v>
+        <v>29.90502908171196</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06180246065656592</v>
+        <v>0.0611718233029275</v>
       </c>
       <c r="W99">
-        <v>0.2212269797771818</v>
+        <v>0.2213756840651697</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3090123032828296</v>
+        <v>0.3058591165146375</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2565269291340265</v>
+        <v>0.2584269291340265</v>
       </c>
       <c r="C100">
-        <v>-1228.473933077105</v>
+        <v>-1247.194034874139</v>
       </c>
       <c r="D100">
-        <v>313.692066922895</v>
+        <v>310.8889651258608</v>
       </c>
       <c r="E100">
-        <v>1276.466</v>
+        <v>1292.383</v>
       </c>
       <c r="F100">
-        <v>1559.866</v>
+        <v>1575.783</v>
       </c>
       <c r="G100">
         <v>17.7</v>
@@ -9481,37 +9481,37 @@
         <v>112.5</v>
       </c>
       <c r="M100">
-        <v>367.8164027999999</v>
+        <v>371.5696314</v>
       </c>
       <c r="N100">
-        <v>-255.3164027999999</v>
+        <v>-259.0696314</v>
       </c>
       <c r="O100">
-        <v>-51.06328055999999</v>
+        <v>-51.81392628</v>
       </c>
       <c r="P100">
-        <v>-204.25312224</v>
+        <v>-207.25570512</v>
       </c>
       <c r="Q100">
-        <v>-159.5531222399999</v>
+        <v>-162.55570512</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.978937937508007</v>
+        <v>3.912075875016015</v>
       </c>
       <c r="T100">
-        <v>29.90502908171196</v>
+        <v>59.81005816342392</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0611718233029275</v>
+        <v>0.06055392609784741</v>
       </c>
       <c r="W100">
-        <v>0.2213756840651697</v>
+        <v>0.2215213842261276</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3058591165146375</v>
+        <v>0.302769630489237</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2584269291340265</v>
-      </c>
-      <c r="C101">
-        <v>-1247.194034874139</v>
-      </c>
-      <c r="D101">
-        <v>310.8889651258608</v>
-      </c>
-      <c r="E101">
-        <v>1292.383</v>
-      </c>
-      <c r="F101">
-        <v>1575.783</v>
-      </c>
-      <c r="G101">
-        <v>17.7</v>
-      </c>
-      <c r="H101">
-        <v>1308.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>157.2</v>
-      </c>
-      <c r="K101">
-        <v>44.7</v>
-      </c>
-      <c r="L101">
-        <v>112.5</v>
-      </c>
-      <c r="M101">
-        <v>371.5696314</v>
-      </c>
-      <c r="N101">
-        <v>-259.0696314</v>
-      </c>
-      <c r="O101">
-        <v>-51.81392628</v>
-      </c>
-      <c r="P101">
-        <v>-207.25570512</v>
-      </c>
-      <c r="Q101">
-        <v>-162.55570512</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.912075875016015</v>
-      </c>
-      <c r="T101">
-        <v>59.81005816342392</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06055392609784741</v>
-      </c>
-      <c r="W101">
-        <v>0.2215213842261276</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.302769630489237</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
